--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438241DC-F5A1-4E5B-86B0-4EA4EAD92291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B3709C-63FB-434A-BE51-C6AC7FA202CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="52">
   <si>
     <t>Aluno</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>5/P</t>
+  </si>
+  <si>
+    <t>5P | F</t>
   </si>
 </sst>
 </file>
@@ -758,7 +761,17 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1096,30 +1109,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.6640625" customWidth="1"/>
+    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1321,7 +1334,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1532,7 +1545,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1774,7 +1787,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -2016,7 +2029,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2258,7 +2271,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2500,7 +2513,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2742,7 +2755,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2984,7 +2997,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3226,7 +3239,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3468,7 +3481,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3710,7 +3723,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3955,7 +3968,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4197,7 +4210,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4439,7 +4452,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4681,7 +4694,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4856,7 +4869,7 @@
         <v>34</v>
       </c>
       <c r="BG16" s="4" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="BH16" s="4"/>
       <c r="BI16" s="4"/>
@@ -4923,7 +4936,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -5165,7 +5178,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5407,7 +5420,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5649,7 +5662,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5891,7 +5904,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -6066,7 +6079,7 @@
         <v>50</v>
       </c>
       <c r="BG21" s="4" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
@@ -6133,7 +6146,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6375,7 +6388,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6617,7 +6630,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6859,7 +6872,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -7101,7 +7114,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7343,7 +7356,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7518,7 +7531,7 @@
         <v>35</v>
       </c>
       <c r="BG27" s="4" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
@@ -7585,7 +7598,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7827,7 +7840,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -8069,7 +8082,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8311,7 +8324,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8553,7 +8566,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8562,33 +8575,38 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB25">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"F"</formula>
+  <conditionalFormatting sqref="BE3:BE31">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:BE31">
+  <conditionalFormatting sqref="BG3:BG31">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BG3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -8599,14 +8617,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8614,7 +8632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8622,7 +8640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8630,7 +8648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8638,7 +8656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8646,7 +8664,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8654,7 +8672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8662,7 +8680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8670,7 +8688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8678,7 +8696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8686,7 +8704,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8694,7 +8712,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8702,7 +8720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8710,7 +8728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8718,7 +8736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8726,7 +8744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8734,7 +8752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8742,7 +8760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8750,7 +8768,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8758,7 +8776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8766,7 +8784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8774,7 +8792,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8782,7 +8800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8790,7 +8808,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8798,7 +8816,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8806,7 +8824,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8814,7 +8832,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8822,7 +8840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8830,7 +8848,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8838,7 +8856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8855,18 +8873,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8874,7 +8892,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8883,7 +8901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8892,7 +8910,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8901,7 +8919,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8910,13 +8928,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8925,7 +8943,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8934,7 +8952,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8950,13 +8968,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8965,7 +8983,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8974,7 +8992,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -8983,7 +9001,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -8992,7 +9010,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -9001,7 +9019,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -9010,7 +9028,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -9019,7 +9037,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -9028,7 +9046,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -9037,7 +9055,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -9046,7 +9064,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -9055,7 +9073,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -9064,7 +9082,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -9073,25 +9091,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -9100,7 +9118,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -9109,7 +9127,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -9118,7 +9136,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B3709C-63FB-434A-BE51-C6AC7FA202CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E45A94F-65DE-4A61-ADD3-F4300C96C793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="52">
   <si>
     <t>Aluno</t>
   </si>
@@ -1109,30 +1109,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.7109375" customWidth="1"/>
+    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1301,8 +1301,12 @@
       <c r="BG1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="BH1" s="7"/>
-      <c r="BI1" s="7"/>
+      <c r="BH1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BI1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="BJ1" s="7"/>
       <c r="BK1" s="7"/>
       <c r="BL1" s="7"/>
@@ -1334,7 +1338,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1512,8 +1516,12 @@
       <c r="BG2" s="7">
         <v>46276</v>
       </c>
-      <c r="BH2" s="1"/>
-      <c r="BI2" s="7"/>
+      <c r="BH2" s="1">
+        <v>46281</v>
+      </c>
+      <c r="BI2" s="7">
+        <v>46283</v>
+      </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="7"/>
       <c r="BL2" s="1"/>
@@ -1545,7 +1553,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1722,8 +1730,12 @@
       <c r="BG3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH3" s="4"/>
-      <c r="BI3" s="4"/>
+      <c r="BH3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
@@ -1787,7 +1799,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -1964,8 +1976,12 @@
       <c r="BG4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH4" s="4"/>
-      <c r="BI4" s="4"/>
+      <c r="BH4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI4" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
@@ -2029,7 +2045,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2206,8 +2222,12 @@
       <c r="BG5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH5" s="4"/>
-      <c r="BI5" s="4"/>
+      <c r="BH5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ5" s="4"/>
       <c r="BK5" s="4"/>
       <c r="BL5" s="4"/>
@@ -2271,7 +2291,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2448,8 +2468,12 @@
       <c r="BG6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH6" s="4"/>
-      <c r="BI6" s="4"/>
+      <c r="BH6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ6" s="4"/>
       <c r="BK6" s="4"/>
       <c r="BL6" s="4"/>
@@ -2513,7 +2537,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2690,8 +2714,12 @@
       <c r="BG7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH7" s="4"/>
-      <c r="BI7" s="4"/>
+      <c r="BH7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ7" s="4"/>
       <c r="BK7" s="4"/>
       <c r="BL7" s="4"/>
@@ -2755,7 +2783,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -2932,8 +2960,12 @@
       <c r="BG8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH8" s="4"/>
-      <c r="BI8" s="4"/>
+      <c r="BH8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ8" s="4"/>
       <c r="BK8" s="4"/>
       <c r="BL8" s="4"/>
@@ -2997,7 +3029,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3174,8 +3206,12 @@
       <c r="BG9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH9" s="4"/>
-      <c r="BI9" s="4"/>
+      <c r="BH9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ9" s="4"/>
       <c r="BK9" s="4"/>
       <c r="BL9" s="4"/>
@@ -3239,7 +3275,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3416,8 +3452,12 @@
       <c r="BG10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH10" s="4"/>
-      <c r="BI10" s="4"/>
+      <c r="BH10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ10" s="4"/>
       <c r="BK10" s="4"/>
       <c r="BL10" s="4"/>
@@ -3481,7 +3521,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3658,8 +3698,12 @@
       <c r="BG11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH11" s="4"/>
-      <c r="BI11" s="4"/>
+      <c r="BH11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI11" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BJ11" s="4"/>
       <c r="BK11" s="4"/>
       <c r="BL11" s="4"/>
@@ -3723,7 +3767,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3903,8 +3947,12 @@
       <c r="BG12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH12" s="4"/>
-      <c r="BI12" s="4"/>
+      <c r="BH12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ12" s="4"/>
       <c r="BK12" s="4"/>
       <c r="BL12" s="4"/>
@@ -3968,7 +4016,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4145,8 +4193,12 @@
       <c r="BG13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH13" s="4"/>
-      <c r="BI13" s="4"/>
+      <c r="BH13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ13" s="4"/>
       <c r="BK13" s="4"/>
       <c r="BL13" s="4"/>
@@ -4210,7 +4262,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4387,8 +4439,12 @@
       <c r="BG14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH14" s="4"/>
-      <c r="BI14" s="4"/>
+      <c r="BH14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ14" s="4"/>
       <c r="BK14" s="4"/>
       <c r="BL14" s="4"/>
@@ -4452,7 +4508,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4629,8 +4685,12 @@
       <c r="BG15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH15" s="4"/>
-      <c r="BI15" s="4"/>
+      <c r="BH15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ15" s="4"/>
       <c r="BK15" s="4"/>
       <c r="BL15" s="4"/>
@@ -4694,7 +4754,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -4871,8 +4931,12 @@
       <c r="BG16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BH16" s="4"/>
-      <c r="BI16" s="4"/>
+      <c r="BH16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ16" s="4"/>
       <c r="BK16" s="4"/>
       <c r="BL16" s="4"/>
@@ -4936,7 +5000,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -5113,8 +5177,12 @@
       <c r="BG17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH17" s="4"/>
-      <c r="BI17" s="4"/>
+      <c r="BH17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ17" s="4"/>
       <c r="BK17" s="4"/>
       <c r="BL17" s="4"/>
@@ -5178,7 +5246,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5355,8 +5423,12 @@
       <c r="BG18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH18" s="4"/>
-      <c r="BI18" s="4"/>
+      <c r="BH18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ18" s="4"/>
       <c r="BK18" s="4"/>
       <c r="BL18" s="4"/>
@@ -5420,7 +5492,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5597,8 +5669,12 @@
       <c r="BG19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH19" s="4"/>
-      <c r="BI19" s="4"/>
+      <c r="BH19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ19" s="4"/>
       <c r="BK19" s="4"/>
       <c r="BL19" s="4"/>
@@ -5662,7 +5738,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5839,8 +5915,12 @@
       <c r="BG20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH20" s="4"/>
-      <c r="BI20" s="4"/>
+      <c r="BH20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ20" s="4"/>
       <c r="BK20" s="4"/>
       <c r="BL20" s="4"/>
@@ -5904,7 +5984,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -6081,8 +6161,12 @@
       <c r="BG21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="BH21" s="4"/>
-      <c r="BI21" s="4"/>
+      <c r="BH21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ21" s="4"/>
       <c r="BK21" s="4"/>
       <c r="BL21" s="4"/>
@@ -6146,7 +6230,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6323,8 +6407,12 @@
       <c r="BG22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH22" s="4"/>
-      <c r="BI22" s="4"/>
+      <c r="BH22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI22" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BJ22" s="4"/>
       <c r="BK22" s="4"/>
       <c r="BL22" s="4"/>
@@ -6388,7 +6476,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6565,8 +6653,12 @@
       <c r="BG23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH23" s="4"/>
-      <c r="BI23" s="4"/>
+      <c r="BH23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ23" s="4"/>
       <c r="BK23" s="4"/>
       <c r="BL23" s="4"/>
@@ -6630,7 +6722,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6807,8 +6899,12 @@
       <c r="BG24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH24" s="4"/>
-      <c r="BI24" s="4"/>
+      <c r="BH24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ24" s="4"/>
       <c r="BK24" s="4"/>
       <c r="BL24" s="4"/>
@@ -6872,7 +6968,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -7049,8 +7145,12 @@
       <c r="BG25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BH25" s="4"/>
-      <c r="BI25" s="4"/>
+      <c r="BH25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ25" s="4"/>
       <c r="BK25" s="4"/>
       <c r="BL25" s="4"/>
@@ -7114,7 +7214,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7291,8 +7391,12 @@
       <c r="BG26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH26" s="4"/>
-      <c r="BI26" s="4"/>
+      <c r="BH26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ26" s="4"/>
       <c r="BK26" s="4"/>
       <c r="BL26" s="4"/>
@@ -7356,7 +7460,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7533,8 +7637,12 @@
       <c r="BG27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="BH27" s="4"/>
-      <c r="BI27" s="4"/>
+      <c r="BH27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ27" s="4"/>
       <c r="BK27" s="4"/>
       <c r="BL27" s="4"/>
@@ -7598,7 +7706,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7775,8 +7883,12 @@
       <c r="BG28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH28" s="4"/>
-      <c r="BI28" s="4"/>
+      <c r="BH28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ28" s="4"/>
       <c r="BK28" s="4"/>
       <c r="BL28" s="4"/>
@@ -7840,7 +7952,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -8017,8 +8129,12 @@
       <c r="BG29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH29" s="4"/>
-      <c r="BI29" s="4"/>
+      <c r="BH29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ29" s="4"/>
       <c r="BK29" s="4"/>
       <c r="BL29" s="4"/>
@@ -8082,7 +8198,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8259,8 +8375,12 @@
       <c r="BG30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH30" s="4"/>
-      <c r="BI30" s="4"/>
+      <c r="BH30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ30" s="4"/>
       <c r="BK30" s="4"/>
       <c r="BL30" s="4"/>
@@ -8324,7 +8444,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8501,8 +8621,12 @@
       <c r="BG31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BH31" s="4"/>
-      <c r="BI31" s="4"/>
+      <c r="BH31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BJ31" s="4"/>
       <c r="BK31" s="4"/>
       <c r="BL31" s="4"/>
@@ -8566,7 +8690,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8574,7 +8698,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
     <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -8617,14 +8741,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8632,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8640,7 +8764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8648,7 +8772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8656,7 +8780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8664,7 +8788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8672,7 +8796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8680,7 +8804,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8688,7 +8812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8696,7 +8820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8704,7 +8828,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8712,7 +8836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8720,7 +8844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8728,7 +8852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8736,7 +8860,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8744,7 +8868,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8752,7 +8876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8760,7 +8884,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8768,7 +8892,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8776,7 +8900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8784,7 +8908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8792,7 +8916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8800,7 +8924,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8808,7 +8932,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8816,7 +8940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8824,7 +8948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8832,7 +8956,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8840,7 +8964,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8848,7 +8972,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8856,7 +8980,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8873,18 +8997,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -8892,7 +9016,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -8901,7 +9025,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -8910,7 +9034,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -8919,7 +9043,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -8928,13 +9052,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -8943,7 +9067,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -8952,7 +9076,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -8968,13 +9092,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -8983,7 +9107,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -8992,7 +9116,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -9001,7 +9125,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -9010,7 +9134,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -9019,7 +9143,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -9028,7 +9152,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -9037,7 +9161,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -9046,7 +9170,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -9055,7 +9179,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -9064,7 +9188,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -9073,7 +9197,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -9082,7 +9206,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -9091,25 +9215,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -9118,7 +9242,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -9127,7 +9251,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -9136,7 +9260,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E45A94F-65DE-4A61-ADD3-F4300C96C793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F4FE13-4B21-499F-BA73-823E8DC575AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -761,7 +761,47 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1109,30 +1149,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.6640625" customWidth="1"/>
+    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1338,7 +1378,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1553,7 +1593,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1799,7 +1839,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -2045,7 +2085,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2291,7 +2331,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2537,7 +2577,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2718,7 +2758,7 @@
         <v>34</v>
       </c>
       <c r="BI7" s="4" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="BJ7" s="4"/>
       <c r="BK7" s="4"/>
@@ -2783,7 +2823,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -3029,7 +3069,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3275,7 +3315,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3521,7 +3561,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3767,7 +3807,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -3951,7 +3991,7 @@
         <v>34</v>
       </c>
       <c r="BI12" s="4" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="BJ12" s="4"/>
       <c r="BK12" s="4"/>
@@ -4016,7 +4056,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4262,7 +4302,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4508,7 +4548,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4754,7 +4794,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -5000,7 +5040,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -5246,7 +5286,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5492,7 +5532,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5738,7 +5778,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -5919,7 +5959,7 @@
         <v>34</v>
       </c>
       <c r="BI20" s="4" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="BJ20" s="4"/>
       <c r="BK20" s="4"/>
@@ -5984,7 +6024,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -6230,7 +6270,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6476,7 +6516,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6722,7 +6762,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -6968,7 +7008,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -7214,7 +7254,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7460,7 +7500,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7706,7 +7746,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -7952,7 +7992,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -8198,7 +8238,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8444,7 +8484,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8690,7 +8730,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8699,38 +8739,53 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE3:BE31">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG3:BG31">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BG3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BI7">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BI7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BI20">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BI20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BI12">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BG3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BI12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -8741,14 +8796,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8756,7 +8811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8764,7 +8819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8772,7 +8827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8780,7 +8835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8788,7 +8843,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8796,7 +8851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8804,7 +8859,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8812,7 +8867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8820,7 +8875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8828,7 +8883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8836,7 +8891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8844,7 +8899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8852,7 +8907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8860,7 +8915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8868,7 +8923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8876,7 +8931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8884,7 +8939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -8892,7 +8947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -8900,7 +8955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -8908,7 +8963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -8916,7 +8971,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -8924,7 +8979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -8932,7 +8987,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -8940,7 +8995,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -8948,7 +9003,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -8956,7 +9011,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -8964,7 +9019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -8972,7 +9027,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -8980,7 +9035,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -8997,18 +9052,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -9016,7 +9071,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -9025,7 +9080,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -9034,7 +9089,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -9043,7 +9098,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -9052,13 +9107,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -9067,7 +9122,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -9076,7 +9131,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -9092,13 +9147,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -9107,7 +9162,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -9116,7 +9171,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -9125,7 +9180,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -9134,7 +9189,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -9143,7 +9198,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -9152,7 +9207,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -9161,7 +9216,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -9170,7 +9225,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -9179,7 +9234,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -9188,7 +9243,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -9197,7 +9252,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -9206,7 +9261,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -9215,25 +9270,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -9242,7 +9297,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -9251,7 +9306,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -9260,7 +9315,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F4FE13-4B21-499F-BA73-823E8DC575AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCF347F-7B63-430D-AA17-AF15C4C76CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="52">
   <si>
     <t>Aluno</t>
   </si>
@@ -761,17 +761,7 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1347,8 +1337,12 @@
       <c r="BI1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="BJ1" s="7"/>
-      <c r="BK1" s="7"/>
+      <c r="BJ1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="BL1" s="7"/>
       <c r="BM1" s="7"/>
       <c r="BN1" s="7"/>
@@ -1562,8 +1556,12 @@
       <c r="BI2" s="7">
         <v>46283</v>
       </c>
-      <c r="BJ2" s="1"/>
-      <c r="BK2" s="7"/>
+      <c r="BJ2" s="1">
+        <v>46288</v>
+      </c>
+      <c r="BK2" s="7">
+        <v>46290</v>
+      </c>
       <c r="BL2" s="1"/>
       <c r="BM2" s="7"/>
       <c r="BN2" s="1"/>
@@ -1776,7 +1774,9 @@
       <c r="BI3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ3" s="4"/>
+      <c r="BJ3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
       <c r="BM3" s="4"/>
@@ -2022,7 +2022,9 @@
       <c r="BI4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BJ4" s="4"/>
+      <c r="BJ4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
       <c r="BM4" s="4"/>
@@ -2268,7 +2270,9 @@
       <c r="BI5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ5" s="4"/>
+      <c r="BJ5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK5" s="4"/>
       <c r="BL5" s="4"/>
       <c r="BM5" s="4"/>
@@ -2514,7 +2518,9 @@
       <c r="BI6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ6" s="4"/>
+      <c r="BJ6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK6" s="4"/>
       <c r="BL6" s="4"/>
       <c r="BM6" s="4"/>
@@ -2760,7 +2766,9 @@
       <c r="BI7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BJ7" s="4"/>
+      <c r="BJ7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK7" s="4"/>
       <c r="BL7" s="4"/>
       <c r="BM7" s="4"/>
@@ -3006,7 +3014,9 @@
       <c r="BI8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ8" s="4"/>
+      <c r="BJ8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK8" s="4"/>
       <c r="BL8" s="4"/>
       <c r="BM8" s="4"/>
@@ -3252,7 +3262,9 @@
       <c r="BI9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ9" s="4"/>
+      <c r="BJ9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK9" s="4"/>
       <c r="BL9" s="4"/>
       <c r="BM9" s="4"/>
@@ -3498,7 +3510,9 @@
       <c r="BI10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ10" s="4"/>
+      <c r="BJ10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK10" s="4"/>
       <c r="BL10" s="4"/>
       <c r="BM10" s="4"/>
@@ -3744,7 +3758,9 @@
       <c r="BI11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BJ11" s="4"/>
+      <c r="BJ11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK11" s="4"/>
       <c r="BL11" s="4"/>
       <c r="BM11" s="4"/>
@@ -3993,7 +4009,9 @@
       <c r="BI12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BJ12" s="4"/>
+      <c r="BJ12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK12" s="4"/>
       <c r="BL12" s="4"/>
       <c r="BM12" s="4"/>
@@ -4239,7 +4257,9 @@
       <c r="BI13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ13" s="4"/>
+      <c r="BJ13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK13" s="4"/>
       <c r="BL13" s="4"/>
       <c r="BM13" s="4"/>
@@ -4485,7 +4505,9 @@
       <c r="BI14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ14" s="4"/>
+      <c r="BJ14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK14" s="4"/>
       <c r="BL14" s="4"/>
       <c r="BM14" s="4"/>
@@ -4731,7 +4753,9 @@
       <c r="BI15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ15" s="4"/>
+      <c r="BJ15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK15" s="4"/>
       <c r="BL15" s="4"/>
       <c r="BM15" s="4"/>
@@ -4977,7 +5001,9 @@
       <c r="BI16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ16" s="4"/>
+      <c r="BJ16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK16" s="4"/>
       <c r="BL16" s="4"/>
       <c r="BM16" s="4"/>
@@ -5223,7 +5249,9 @@
       <c r="BI17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ17" s="4"/>
+      <c r="BJ17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK17" s="4"/>
       <c r="BL17" s="4"/>
       <c r="BM17" s="4"/>
@@ -5469,7 +5497,9 @@
       <c r="BI18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ18" s="4"/>
+      <c r="BJ18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK18" s="4"/>
       <c r="BL18" s="4"/>
       <c r="BM18" s="4"/>
@@ -5715,7 +5745,9 @@
       <c r="BI19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ19" s="4"/>
+      <c r="BJ19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK19" s="4"/>
       <c r="BL19" s="4"/>
       <c r="BM19" s="4"/>
@@ -5961,7 +5993,9 @@
       <c r="BI20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BJ20" s="4"/>
+      <c r="BJ20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK20" s="4"/>
       <c r="BL20" s="4"/>
       <c r="BM20" s="4"/>
@@ -6207,7 +6241,9 @@
       <c r="BI21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ21" s="4"/>
+      <c r="BJ21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK21" s="4"/>
       <c r="BL21" s="4"/>
       <c r="BM21" s="4"/>
@@ -6453,7 +6489,9 @@
       <c r="BI22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BJ22" s="4"/>
+      <c r="BJ22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK22" s="4"/>
       <c r="BL22" s="4"/>
       <c r="BM22" s="4"/>
@@ -6699,7 +6737,9 @@
       <c r="BI23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ23" s="4"/>
+      <c r="BJ23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK23" s="4"/>
       <c r="BL23" s="4"/>
       <c r="BM23" s="4"/>
@@ -6945,7 +6985,9 @@
       <c r="BI24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ24" s="4"/>
+      <c r="BJ24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK24" s="4"/>
       <c r="BL24" s="4"/>
       <c r="BM24" s="4"/>
@@ -7191,7 +7233,9 @@
       <c r="BI25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ25" s="4"/>
+      <c r="BJ25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK25" s="4"/>
       <c r="BL25" s="4"/>
       <c r="BM25" s="4"/>
@@ -7437,7 +7481,9 @@
       <c r="BI26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ26" s="4"/>
+      <c r="BJ26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK26" s="4"/>
       <c r="BL26" s="4"/>
       <c r="BM26" s="4"/>
@@ -7683,7 +7729,9 @@
       <c r="BI27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ27" s="4"/>
+      <c r="BJ27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK27" s="4"/>
       <c r="BL27" s="4"/>
       <c r="BM27" s="4"/>
@@ -7929,7 +7977,9 @@
       <c r="BI28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ28" s="4"/>
+      <c r="BJ28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK28" s="4"/>
       <c r="BL28" s="4"/>
       <c r="BM28" s="4"/>
@@ -8175,7 +8225,9 @@
       <c r="BI29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ29" s="4"/>
+      <c r="BJ29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK29" s="4"/>
       <c r="BL29" s="4"/>
       <c r="BM29" s="4"/>
@@ -8421,7 +8473,9 @@
       <c r="BI30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ30" s="4"/>
+      <c r="BJ30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK30" s="4"/>
       <c r="BL30" s="4"/>
       <c r="BM30" s="4"/>
@@ -8667,7 +8721,9 @@
       <c r="BI31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BJ31" s="4"/>
+      <c r="BJ31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BK31" s="4"/>
       <c r="BL31" s="4"/>
       <c r="BM31" s="4"/>
@@ -8738,38 +8794,38 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE3:BE31">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG3:BG31">
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BG3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8778,14 +8834,14 @@
       <formula>NOT(ISERROR(SEARCH("F",BI7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI20">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BI20)))</formula>
+  <conditionalFormatting sqref="BI12">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BI12)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI12">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BI12)))</formula>
+  <conditionalFormatting sqref="BI20">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BI20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCF347F-7B63-430D-AA17-AF15C4C76CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442BC47D-1C68-432E-8204-1F19F04CC781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -1139,30 +1139,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.7109375" customWidth="1"/>
+    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1591,7 +1591,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1839,7 +1839,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -2087,7 +2087,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2335,7 +2335,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2583,7 +2583,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2831,7 +2831,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -3079,7 +3079,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3327,7 +3327,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3575,7 +3575,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3823,7 +3823,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -4074,7 +4074,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4322,7 +4322,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4570,7 +4570,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4818,7 +4818,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -5066,7 +5066,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -5314,7 +5314,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5562,7 +5562,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5810,7 +5810,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -6058,7 +6058,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -6306,7 +6306,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6554,7 +6554,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6802,7 +6802,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -7050,7 +7050,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -7298,7 +7298,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7546,7 +7546,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7794,7 +7794,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -8042,7 +8042,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -8290,7 +8290,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8538,7 +8538,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8786,7 +8786,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8852,14 +8852,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8939,7 +8939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -8971,7 +8971,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -8987,7 +8987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -9059,7 +9059,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -9108,18 +9108,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -9136,7 +9136,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -9145,7 +9145,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -9154,7 +9154,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -9163,13 +9163,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -9178,7 +9178,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -9187,7 +9187,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -9203,13 +9203,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -9218,7 +9218,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -9227,7 +9227,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -9236,7 +9236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -9245,7 +9245,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -9254,7 +9254,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -9263,7 +9263,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -9272,7 +9272,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -9281,7 +9281,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -9290,7 +9290,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -9299,7 +9299,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -9308,7 +9308,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -9317,7 +9317,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -9326,25 +9326,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -9353,7 +9353,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -9362,7 +9362,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -9371,7 +9371,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442BC47D-1C68-432E-8204-1F19F04CC781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E63785-81C5-4489-8BDE-B19FD6D907E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="52">
   <si>
     <t>Aluno</t>
   </si>
@@ -1777,7 +1777,9 @@
       <c r="BJ3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK3" s="4"/>
+      <c r="BK3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL3" s="4"/>
       <c r="BM3" s="4"/>
       <c r="BN3" s="4"/>
@@ -2025,7 +2027,9 @@
       <c r="BJ4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK4" s="4"/>
+      <c r="BK4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL4" s="4"/>
       <c r="BM4" s="4"/>
       <c r="BN4" s="4"/>
@@ -2273,7 +2277,9 @@
       <c r="BJ5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK5" s="4"/>
+      <c r="BK5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL5" s="4"/>
       <c r="BM5" s="4"/>
       <c r="BN5" s="4"/>
@@ -2521,7 +2527,9 @@
       <c r="BJ6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK6" s="4"/>
+      <c r="BK6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL6" s="4"/>
       <c r="BM6" s="4"/>
       <c r="BN6" s="4"/>
@@ -2769,7 +2777,9 @@
       <c r="BJ7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK7" s="4"/>
+      <c r="BK7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL7" s="4"/>
       <c r="BM7" s="4"/>
       <c r="BN7" s="4"/>
@@ -3017,7 +3027,9 @@
       <c r="BJ8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK8" s="4"/>
+      <c r="BK8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL8" s="4"/>
       <c r="BM8" s="4"/>
       <c r="BN8" s="4"/>
@@ -3265,7 +3277,9 @@
       <c r="BJ9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK9" s="4"/>
+      <c r="BK9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL9" s="4"/>
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
@@ -3513,7 +3527,9 @@
       <c r="BJ10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK10" s="4"/>
+      <c r="BK10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL10" s="4"/>
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
@@ -3761,7 +3777,9 @@
       <c r="BJ11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK11" s="4"/>
+      <c r="BK11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL11" s="4"/>
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
@@ -4012,7 +4030,9 @@
       <c r="BJ12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK12" s="4"/>
+      <c r="BK12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL12" s="4"/>
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
@@ -4260,7 +4280,9 @@
       <c r="BJ13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK13" s="4"/>
+      <c r="BK13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL13" s="4"/>
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
@@ -4508,7 +4530,9 @@
       <c r="BJ14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK14" s="4"/>
+      <c r="BK14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL14" s="4"/>
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
@@ -4756,7 +4780,9 @@
       <c r="BJ15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK15" s="4"/>
+      <c r="BK15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL15" s="4"/>
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
@@ -5004,7 +5030,9 @@
       <c r="BJ16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK16" s="4"/>
+      <c r="BK16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL16" s="4"/>
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
@@ -5252,7 +5280,9 @@
       <c r="BJ17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK17" s="4"/>
+      <c r="BK17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL17" s="4"/>
       <c r="BM17" s="4"/>
       <c r="BN17" s="4"/>
@@ -5500,7 +5530,9 @@
       <c r="BJ18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK18" s="4"/>
+      <c r="BK18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL18" s="4"/>
       <c r="BM18" s="4"/>
       <c r="BN18" s="4"/>
@@ -5748,7 +5780,9 @@
       <c r="BJ19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK19" s="4"/>
+      <c r="BK19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL19" s="4"/>
       <c r="BM19" s="4"/>
       <c r="BN19" s="4"/>
@@ -5996,7 +6030,9 @@
       <c r="BJ20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK20" s="4"/>
+      <c r="BK20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL20" s="4"/>
       <c r="BM20" s="4"/>
       <c r="BN20" s="4"/>
@@ -6244,7 +6280,9 @@
       <c r="BJ21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK21" s="4"/>
+      <c r="BK21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL21" s="4"/>
       <c r="BM21" s="4"/>
       <c r="BN21" s="4"/>
@@ -6492,7 +6530,9 @@
       <c r="BJ22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK22" s="4"/>
+      <c r="BK22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL22" s="4"/>
       <c r="BM22" s="4"/>
       <c r="BN22" s="4"/>
@@ -6740,7 +6780,9 @@
       <c r="BJ23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK23" s="4"/>
+      <c r="BK23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL23" s="4"/>
       <c r="BM23" s="4"/>
       <c r="BN23" s="4"/>
@@ -6988,7 +7030,9 @@
       <c r="BJ24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK24" s="4"/>
+      <c r="BK24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL24" s="4"/>
       <c r="BM24" s="4"/>
       <c r="BN24" s="4"/>
@@ -7236,7 +7280,9 @@
       <c r="BJ25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK25" s="4"/>
+      <c r="BK25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL25" s="4"/>
       <c r="BM25" s="4"/>
       <c r="BN25" s="4"/>
@@ -7484,7 +7530,9 @@
       <c r="BJ26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK26" s="4"/>
+      <c r="BK26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL26" s="4"/>
       <c r="BM26" s="4"/>
       <c r="BN26" s="4"/>
@@ -7732,7 +7780,9 @@
       <c r="BJ27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK27" s="4"/>
+      <c r="BK27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL27" s="4"/>
       <c r="BM27" s="4"/>
       <c r="BN27" s="4"/>
@@ -7980,7 +8030,9 @@
       <c r="BJ28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK28" s="4"/>
+      <c r="BK28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL28" s="4"/>
       <c r="BM28" s="4"/>
       <c r="BN28" s="4"/>
@@ -8228,7 +8280,9 @@
       <c r="BJ29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK29" s="4"/>
+      <c r="BK29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL29" s="4"/>
       <c r="BM29" s="4"/>
       <c r="BN29" s="4"/>
@@ -8476,7 +8530,9 @@
       <c r="BJ30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK30" s="4"/>
+      <c r="BK30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL30" s="4"/>
       <c r="BM30" s="4"/>
       <c r="BN30" s="4"/>
@@ -8724,7 +8780,9 @@
       <c r="BJ31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BK31" s="4"/>
+      <c r="BK31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BL31" s="4"/>
       <c r="BM31" s="4"/>
       <c r="BN31" s="4"/>
@@ -8794,7 +8852,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
     <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E63785-81C5-4489-8BDE-B19FD6D907E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5D84DD-7DC3-4C59-A7F8-D3D0718744BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="52">
   <si>
     <t>Aluno</t>
   </si>
@@ -1139,30 +1139,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS32"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.6640625" customWidth="1"/>
+    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1343,8 +1343,12 @@
       <c r="BK1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="BL1" s="7"/>
-      <c r="BM1" s="7"/>
+      <c r="BL1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BM1" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="BN1" s="7"/>
       <c r="BO1" s="7"/>
       <c r="BP1" s="7"/>
@@ -1372,7 +1376,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1562,8 +1566,12 @@
       <c r="BK2" s="7">
         <v>46290</v>
       </c>
-      <c r="BL2" s="1"/>
-      <c r="BM2" s="7"/>
+      <c r="BL2" s="1">
+        <v>46295</v>
+      </c>
+      <c r="BM2" s="7">
+        <v>46297</v>
+      </c>
       <c r="BN2" s="1"/>
       <c r="BO2" s="7"/>
       <c r="BP2" s="1"/>
@@ -1591,7 +1599,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25130313</v>
@@ -1780,7 +1788,9 @@
       <c r="BK3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL3" s="4"/>
+      <c r="BL3" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM3" s="4"/>
       <c r="BN3" s="4"/>
       <c r="BO3" s="4"/>
@@ -1841,7 +1851,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129077</v>
@@ -2030,7 +2040,9 @@
       <c r="BK4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL4" s="4"/>
+      <c r="BL4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM4" s="4"/>
       <c r="BN4" s="4"/>
       <c r="BO4" s="4"/>
@@ -2091,7 +2103,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129045</v>
@@ -2280,7 +2292,9 @@
       <c r="BK5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL5" s="4"/>
+      <c r="BL5" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM5" s="4"/>
       <c r="BN5" s="4"/>
       <c r="BO5" s="4"/>
@@ -2341,7 +2355,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129967</v>
@@ -2530,7 +2544,9 @@
       <c r="BK6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL6" s="4"/>
+      <c r="BL6" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM6" s="4"/>
       <c r="BN6" s="4"/>
       <c r="BO6" s="4"/>
@@ -2591,7 +2607,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129049</v>
@@ -2780,7 +2796,9 @@
       <c r="BK7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL7" s="4"/>
+      <c r="BL7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM7" s="4"/>
       <c r="BN7" s="4"/>
       <c r="BO7" s="4"/>
@@ -2841,7 +2859,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129051</v>
@@ -3030,7 +3048,9 @@
       <c r="BK8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL8" s="4"/>
+      <c r="BL8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM8" s="4"/>
       <c r="BN8" s="4"/>
       <c r="BO8" s="4"/>
@@ -3091,7 +3111,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129087</v>
@@ -3280,7 +3300,9 @@
       <c r="BK9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL9" s="4"/>
+      <c r="BL9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
       <c r="BO9" s="4"/>
@@ -3341,7 +3363,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129053</v>
@@ -3530,7 +3552,9 @@
       <c r="BK10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL10" s="4"/>
+      <c r="BL10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
       <c r="BO10" s="4"/>
@@ -3591,7 +3615,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129055</v>
@@ -3780,7 +3804,9 @@
       <c r="BK11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL11" s="4"/>
+      <c r="BL11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
       <c r="BO11" s="4"/>
@@ -3841,7 +3867,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129178</v>
@@ -4033,7 +4059,9 @@
       <c r="BK12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL12" s="4"/>
+      <c r="BL12" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
       <c r="BO12" s="4"/>
@@ -4094,7 +4122,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129089</v>
@@ -4283,7 +4311,9 @@
       <c r="BK13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL13" s="4"/>
+      <c r="BL13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
       <c r="BO13" s="4"/>
@@ -4344,7 +4374,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129057</v>
@@ -4533,7 +4563,9 @@
       <c r="BK14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL14" s="4"/>
+      <c r="BL14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
       <c r="BO14" s="4"/>
@@ -4594,7 +4626,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129091</v>
@@ -4783,7 +4815,9 @@
       <c r="BK15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL15" s="4"/>
+      <c r="BL15" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
       <c r="BO15" s="4"/>
@@ -4844,7 +4878,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129123</v>
@@ -5033,7 +5067,9 @@
       <c r="BK16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL16" s="4"/>
+      <c r="BL16" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
       <c r="BO16" s="4"/>
@@ -5094,7 +5130,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129059</v>
@@ -5283,7 +5319,9 @@
       <c r="BK17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL17" s="4"/>
+      <c r="BL17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM17" s="4"/>
       <c r="BN17" s="4"/>
       <c r="BO17" s="4"/>
@@ -5344,7 +5382,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129061</v>
@@ -5533,7 +5571,9 @@
       <c r="BK18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL18" s="4"/>
+      <c r="BL18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM18" s="4"/>
       <c r="BN18" s="4"/>
       <c r="BO18" s="4"/>
@@ -5594,7 +5634,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129095</v>
@@ -5783,7 +5823,9 @@
       <c r="BK19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL19" s="4"/>
+      <c r="BL19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM19" s="4"/>
       <c r="BN19" s="4"/>
       <c r="BO19" s="4"/>
@@ -5844,7 +5886,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25130299</v>
@@ -6033,7 +6075,9 @@
       <c r="BK20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL20" s="4"/>
+      <c r="BL20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM20" s="4"/>
       <c r="BN20" s="4"/>
       <c r="BO20" s="4"/>
@@ -6094,7 +6138,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129249</v>
@@ -6283,7 +6327,9 @@
       <c r="BK21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL21" s="4"/>
+      <c r="BL21" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="BM21" s="4"/>
       <c r="BN21" s="4"/>
       <c r="BO21" s="4"/>
@@ -6344,7 +6390,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129970</v>
@@ -6533,7 +6579,9 @@
       <c r="BK22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL22" s="4"/>
+      <c r="BL22" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="BM22" s="4"/>
       <c r="BN22" s="4"/>
       <c r="BO22" s="4"/>
@@ -6594,7 +6642,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25130290</v>
@@ -6783,7 +6831,9 @@
       <c r="BK23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL23" s="4"/>
+      <c r="BL23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM23" s="4"/>
       <c r="BN23" s="4"/>
       <c r="BO23" s="4"/>
@@ -6844,7 +6894,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129129</v>
@@ -7033,7 +7083,9 @@
       <c r="BK24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL24" s="4"/>
+      <c r="BL24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM24" s="4"/>
       <c r="BN24" s="4"/>
       <c r="BO24" s="4"/>
@@ -7094,7 +7146,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129237</v>
@@ -7283,7 +7335,9 @@
       <c r="BK25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL25" s="4"/>
+      <c r="BL25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM25" s="4"/>
       <c r="BN25" s="4"/>
       <c r="BO25" s="4"/>
@@ -7344,7 +7398,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129063</v>
@@ -7533,7 +7587,9 @@
       <c r="BK26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL26" s="4"/>
+      <c r="BL26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM26" s="4"/>
       <c r="BN26" s="4"/>
       <c r="BO26" s="4"/>
@@ -7594,7 +7650,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129065</v>
@@ -7783,7 +7839,9 @@
       <c r="BK27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL27" s="4"/>
+      <c r="BL27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM27" s="4"/>
       <c r="BN27" s="4"/>
       <c r="BO27" s="4"/>
@@ -7844,7 +7902,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129182</v>
@@ -8033,7 +8091,9 @@
       <c r="BK28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL28" s="4"/>
+      <c r="BL28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM28" s="4"/>
       <c r="BN28" s="4"/>
       <c r="BO28" s="4"/>
@@ -8094,7 +8154,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129103</v>
@@ -8283,7 +8343,9 @@
       <c r="BK29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL29" s="4"/>
+      <c r="BL29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM29" s="4"/>
       <c r="BN29" s="4"/>
       <c r="BO29" s="4"/>
@@ -8344,7 +8406,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129131</v>
@@ -8533,7 +8595,9 @@
       <c r="BK30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL30" s="4"/>
+      <c r="BL30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM30" s="4"/>
       <c r="BN30" s="4"/>
       <c r="BO30" s="4"/>
@@ -8594,7 +8658,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129099</v>
@@ -8783,7 +8847,9 @@
       <c r="BK31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BL31" s="4"/>
+      <c r="BL31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BM31" s="4"/>
       <c r="BN31" s="4"/>
       <c r="BO31" s="4"/>
@@ -8844,7 +8910,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="BD32" s="8"/>
     </row>
   </sheetData>
@@ -8852,7 +8918,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
     <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -8910,14 +8976,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8925,7 +8991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25130313</v>
       </c>
@@ -8933,7 +8999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129077</v>
       </c>
@@ -8941,7 +9007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129045</v>
       </c>
@@ -8949,7 +9015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129967</v>
       </c>
@@ -8957,7 +9023,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129049</v>
       </c>
@@ -8965,7 +9031,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129051</v>
       </c>
@@ -8973,7 +9039,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129087</v>
       </c>
@@ -8981,7 +9047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129053</v>
       </c>
@@ -8989,7 +9055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129055</v>
       </c>
@@ -8997,7 +9063,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129178</v>
       </c>
@@ -9005,7 +9071,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129089</v>
       </c>
@@ -9013,7 +9079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129057</v>
       </c>
@@ -9021,7 +9087,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129091</v>
       </c>
@@ -9029,7 +9095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129123</v>
       </c>
@@ -9037,7 +9103,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129059</v>
       </c>
@@ -9045,7 +9111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129061</v>
       </c>
@@ -9053,7 +9119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129095</v>
       </c>
@@ -9061,7 +9127,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25130299</v>
       </c>
@@ -9069,7 +9135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129249</v>
       </c>
@@ -9077,7 +9143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129970</v>
       </c>
@@ -9085,7 +9151,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25130290</v>
       </c>
@@ -9093,7 +9159,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129129</v>
       </c>
@@ -9101,7 +9167,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129237</v>
       </c>
@@ -9109,7 +9175,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129063</v>
       </c>
@@ -9117,7 +9183,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129065</v>
       </c>
@@ -9125,7 +9191,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129182</v>
       </c>
@@ -9133,7 +9199,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129103</v>
       </c>
@@ -9141,7 +9207,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129131</v>
       </c>
@@ -9149,7 +9215,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129099</v>
       </c>
@@ -9166,18 +9232,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -9185,7 +9251,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -9194,7 +9260,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -9203,7 +9269,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -9212,7 +9278,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paulo Saouza</v>
@@ -9221,13 +9287,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -9236,7 +9302,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -9245,7 +9311,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
@@ -9261,13 +9327,13 @@
         <v>36.011080332409975</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -9276,7 +9342,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -9285,7 +9351,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -9294,7 +9360,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -9303,7 +9369,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>
@@ -9312,7 +9378,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Luís Henrique Preira da Silva</v>
@@ -9321,7 +9387,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Luís Otávio Scorcer da Silva</v>
@@ -9330,7 +9396,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Luiza Amaral Corazin</v>
@@ -9339,7 +9405,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Maria Fernanda Moraes de Oliveira</v>
@@ -9348,7 +9414,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Mariana Costa de Carvalho</v>
@@ -9357,7 +9423,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Defendi</v>
@@ -9366,7 +9432,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Henrique Salles Spineli</v>
@@ -9375,7 +9441,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Miguel Araujo Gerbi</v>
@@ -9384,25 +9450,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Mirella Sampaio Vicente</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Murilo Jordan Cezar</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Otávio Moreira Benedeti</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Pietra Vitória Fernandes Lopes</v>
@@ -9411,7 +9477,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Sayury de Moraes Araujo</v>
@@ -9420,7 +9486,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Tamires Guarizzo</v>
@@ -9429,7 +9495,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Vicenzo Vieira Varandas</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A59EF08-6451-4DDD-9308-47C368351B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75D7B49-1D7D-4EDC-94C0-88FC8D909247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="53">
   <si>
     <t>Aluno</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Francisco de Paula Souza</t>
+  </si>
+  <si>
+    <t>P/5F</t>
   </si>
 </sst>
 </file>
@@ -761,7 +764,117 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2808,7 +2921,7 @@
         <v>33</v>
       </c>
       <c r="BM7" s="4" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="BN7" s="4"/>
       <c r="BO7" s="4"/>
@@ -8977,53 +9090,58 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="13" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="19" priority="12" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE3:BE31">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG3:BG31">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BG3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI7">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI12">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI20">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BM1:BM1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BM1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75D7B49-1D7D-4EDC-94C0-88FC8D909247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549FB9A9-86A8-4B02-A206-05001F14858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
     <sheet name="alunos" sheetId="2" r:id="rId2"/>
     <sheet name="vistos" sheetId="3" r:id="rId3"/>
+    <sheet name="Atividade EXPO" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -195,6 +196,12 @@
   </si>
   <si>
     <t>P/5F</t>
+  </si>
+  <si>
+    <t>VISTO</t>
+  </si>
+  <si>
+    <t>✅</t>
   </si>
 </sst>
 </file>
@@ -706,7 +713,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -718,6 +725,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -764,97 +774,7 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1462,7 +1382,9 @@
       <c r="BM1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BN1" s="7"/>
+      <c r="BN1" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="BO1" s="7"/>
       <c r="BP1" s="7"/>
       <c r="BQ1" s="7"/>
@@ -1685,7 +1607,9 @@
       <c r="BM2" s="7">
         <v>46297</v>
       </c>
-      <c r="BN2" s="1"/>
+      <c r="BN2" s="1">
+        <v>46302</v>
+      </c>
       <c r="BO2" s="7"/>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="7"/>
@@ -1907,7 +1831,9 @@
       <c r="BM3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN3" s="4"/>
+      <c r="BN3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO3" s="4"/>
       <c r="BP3" s="4"/>
       <c r="BQ3" s="4"/>
@@ -2161,7 +2087,9 @@
       <c r="BM4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN4" s="4"/>
+      <c r="BN4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO4" s="4"/>
       <c r="BP4" s="4"/>
       <c r="BQ4" s="4"/>
@@ -2415,7 +2343,9 @@
       <c r="BM5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN5" s="4"/>
+      <c r="BN5" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO5" s="4"/>
       <c r="BP5" s="4"/>
       <c r="BQ5" s="4"/>
@@ -2669,7 +2599,9 @@
       <c r="BM6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN6" s="4"/>
+      <c r="BN6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO6" s="4"/>
       <c r="BP6" s="4"/>
       <c r="BQ6" s="4"/>
@@ -2923,7 +2855,9 @@
       <c r="BM7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="BN7" s="4"/>
+      <c r="BN7" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO7" s="4"/>
       <c r="BP7" s="4"/>
       <c r="BQ7" s="4"/>
@@ -3177,7 +3111,9 @@
       <c r="BM8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN8" s="4"/>
+      <c r="BN8" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO8" s="4"/>
       <c r="BP8" s="4"/>
       <c r="BQ8" s="4"/>
@@ -3431,7 +3367,9 @@
       <c r="BM9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN9" s="4"/>
+      <c r="BN9" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO9" s="4"/>
       <c r="BP9" s="4"/>
       <c r="BQ9" s="4"/>
@@ -3685,7 +3623,9 @@
       <c r="BM10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN10" s="4"/>
+      <c r="BN10" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO10" s="4"/>
       <c r="BP10" s="4"/>
       <c r="BQ10" s="4"/>
@@ -3939,7 +3879,9 @@
       <c r="BM11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN11" s="4"/>
+      <c r="BN11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO11" s="4"/>
       <c r="BP11" s="4"/>
       <c r="BQ11" s="4"/>
@@ -4196,7 +4138,9 @@
       <c r="BM12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN12" s="4"/>
+      <c r="BN12" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO12" s="4"/>
       <c r="BP12" s="4"/>
       <c r="BQ12" s="4"/>
@@ -4450,7 +4394,9 @@
       <c r="BM13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN13" s="4"/>
+      <c r="BN13" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO13" s="4"/>
       <c r="BP13" s="4"/>
       <c r="BQ13" s="4"/>
@@ -4704,7 +4650,9 @@
       <c r="BM14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN14" s="4"/>
+      <c r="BN14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO14" s="4"/>
       <c r="BP14" s="4"/>
       <c r="BQ14" s="4"/>
@@ -4958,7 +4906,9 @@
       <c r="BM15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN15" s="4"/>
+      <c r="BN15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO15" s="4"/>
       <c r="BP15" s="4"/>
       <c r="BQ15" s="4"/>
@@ -5212,7 +5162,9 @@
       <c r="BM16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN16" s="4"/>
+      <c r="BN16" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO16" s="4"/>
       <c r="BP16" s="4"/>
       <c r="BQ16" s="4"/>
@@ -5466,7 +5418,9 @@
       <c r="BM17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN17" s="4"/>
+      <c r="BN17" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO17" s="4"/>
       <c r="BP17" s="4"/>
       <c r="BQ17" s="4"/>
@@ -5720,7 +5674,9 @@
       <c r="BM18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN18" s="4"/>
+      <c r="BN18" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO18" s="4"/>
       <c r="BP18" s="4"/>
       <c r="BQ18" s="4"/>
@@ -5974,7 +5930,9 @@
       <c r="BM19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN19" s="4"/>
+      <c r="BN19" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO19" s="4"/>
       <c r="BP19" s="4"/>
       <c r="BQ19" s="4"/>
@@ -6228,7 +6186,9 @@
       <c r="BM20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN20" s="4"/>
+      <c r="BN20" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO20" s="4"/>
       <c r="BP20" s="4"/>
       <c r="BQ20" s="4"/>
@@ -6482,7 +6442,9 @@
       <c r="BM21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN21" s="4"/>
+      <c r="BN21" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO21" s="4"/>
       <c r="BP21" s="4"/>
       <c r="BQ21" s="4"/>
@@ -6736,7 +6698,9 @@
       <c r="BM22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BN22" s="4"/>
+      <c r="BN22" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO22" s="4"/>
       <c r="BP22" s="4"/>
       <c r="BQ22" s="4"/>
@@ -6990,7 +6954,9 @@
       <c r="BM23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN23" s="4"/>
+      <c r="BN23" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO23" s="4"/>
       <c r="BP23" s="4"/>
       <c r="BQ23" s="4"/>
@@ -7244,7 +7210,9 @@
       <c r="BM24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN24" s="4"/>
+      <c r="BN24" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO24" s="4"/>
       <c r="BP24" s="4"/>
       <c r="BQ24" s="4"/>
@@ -7498,7 +7466,9 @@
       <c r="BM25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN25" s="4"/>
+      <c r="BN25" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO25" s="4"/>
       <c r="BP25" s="4"/>
       <c r="BQ25" s="4"/>
@@ -7752,7 +7722,9 @@
       <c r="BM26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN26" s="4"/>
+      <c r="BN26" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO26" s="4"/>
       <c r="BP26" s="4"/>
       <c r="BQ26" s="4"/>
@@ -8006,7 +7978,9 @@
       <c r="BM27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN27" s="4"/>
+      <c r="BN27" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO27" s="4"/>
       <c r="BP27" s="4"/>
       <c r="BQ27" s="4"/>
@@ -8260,7 +8234,9 @@
       <c r="BM28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN28" s="4"/>
+      <c r="BN28" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO28" s="4"/>
       <c r="BP28" s="4"/>
       <c r="BQ28" s="4"/>
@@ -8514,7 +8490,9 @@
       <c r="BM29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN29" s="4"/>
+      <c r="BN29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO29" s="4"/>
       <c r="BP29" s="4"/>
       <c r="BQ29" s="4"/>
@@ -8768,7 +8746,9 @@
       <c r="BM30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN30" s="4"/>
+      <c r="BN30" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO30" s="4"/>
       <c r="BP30" s="4"/>
       <c r="BQ30" s="4"/>
@@ -9022,7 +9002,9 @@
       <c r="BM31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BN31" s="4"/>
+      <c r="BN31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BO31" s="4"/>
       <c r="BP31" s="4"/>
       <c r="BQ31" s="4"/>
@@ -9089,59 +9071,64 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
-    <cfRule type="cellIs" dxfId="20" priority="13" operator="equal">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="19" priority="12" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE3:BE31">
-    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG3:BG31">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BG3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI7">
-    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI12">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI20">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM1:BM1048576">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BM1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BN3:BN31">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BM1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BN3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -9683,4 +9670,257 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FF6044-FA9D-4667-8C93-8D745C91A49A}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549FB9A9-86A8-4B02-A206-05001F14858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38124035-33F2-43E5-8837-DFD5087DA78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -1385,7 +1385,9 @@
       <c r="BN1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="BO1" s="7"/>
+      <c r="BO1" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="BP1" s="7"/>
       <c r="BQ1" s="7"/>
       <c r="BR1" s="7"/>
@@ -1610,7 +1612,9 @@
       <c r="BN2" s="1">
         <v>46302</v>
       </c>
-      <c r="BO2" s="7"/>
+      <c r="BO2" s="7">
+        <v>910</v>
+      </c>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="7"/>
       <c r="BR2" s="1"/>
@@ -9071,7 +9075,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
     <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9394,19 +9398,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4775B77-1C5A-4CFC-B6A0-BD404AF384A2}">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -9414,7 +9418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Beatriz Albuquerque Marcondes Dos Santos</v>
@@ -9423,7 +9427,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Clara Andrzejewky Antonacci</v>
@@ -9432,7 +9436,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Elisa Marielle de Oliveira Carvalho</v>
@@ -9441,7 +9445,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Francisco de Paula Souza</v>
@@ -9450,13 +9454,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Gabriela Caroline da Silva</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Giovana Corrêa</v>
@@ -9465,7 +9469,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Ítalo Mozer de Souza</v>
@@ -9474,29 +9478,19 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>João Vitor Franco Tandello</v>
       </c>
-      <c r="K10">
-        <v>130</v>
-      </c>
-      <c r="L10">
-        <v>1.9</v>
-      </c>
-      <c r="M10">
-        <f>K10/(L10*L10)</f>
-        <v>36.011080332409975</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Júlia Gabrielly da Silva Gonzaga</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Julia Novo de Souza</v>
@@ -9505,7 +9499,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Juliano Rafael Brolezzi Moraes</v>
@@ -9514,7 +9508,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Kaique Gonçanvel Pavan</v>
@@ -9523,7 +9517,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Leandro Saltorato Júnior</v>
@@ -9532,7 +9526,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Letícia Corrêa da Silva</v>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38124035-33F2-43E5-8837-DFD5087DA78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55EDA375-B9F0-4C8D-B291-CD5779F5BD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -1613,7 +1613,7 @@
         <v>46302</v>
       </c>
       <c r="BO2" s="7">
-        <v>910</v>
+        <v>46304</v>
       </c>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="7"/>
@@ -1838,7 +1838,9 @@
       <c r="BN3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO3" s="4"/>
+      <c r="BO3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP3" s="4"/>
       <c r="BQ3" s="4"/>
       <c r="BR3" s="4"/>
@@ -2094,7 +2096,9 @@
       <c r="BN4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO4" s="4"/>
+      <c r="BO4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP4" s="4"/>
       <c r="BQ4" s="4"/>
       <c r="BR4" s="4"/>
@@ -2350,7 +2354,9 @@
       <c r="BN5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO5" s="4"/>
+      <c r="BO5" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP5" s="4"/>
       <c r="BQ5" s="4"/>
       <c r="BR5" s="4"/>
@@ -2606,7 +2612,9 @@
       <c r="BN6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO6" s="4"/>
+      <c r="BO6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP6" s="4"/>
       <c r="BQ6" s="4"/>
       <c r="BR6" s="4"/>
@@ -2862,7 +2870,9 @@
       <c r="BN7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO7" s="4"/>
+      <c r="BO7" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP7" s="4"/>
       <c r="BQ7" s="4"/>
       <c r="BR7" s="4"/>
@@ -3118,7 +3128,9 @@
       <c r="BN8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO8" s="4"/>
+      <c r="BO8" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP8" s="4"/>
       <c r="BQ8" s="4"/>
       <c r="BR8" s="4"/>
@@ -3374,7 +3386,9 @@
       <c r="BN9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO9" s="4"/>
+      <c r="BO9" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP9" s="4"/>
       <c r="BQ9" s="4"/>
       <c r="BR9" s="4"/>
@@ -3630,7 +3644,9 @@
       <c r="BN10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO10" s="4"/>
+      <c r="BO10" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP10" s="4"/>
       <c r="BQ10" s="4"/>
       <c r="BR10" s="4"/>
@@ -3886,7 +3902,9 @@
       <c r="BN11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO11" s="4"/>
+      <c r="BO11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP11" s="4"/>
       <c r="BQ11" s="4"/>
       <c r="BR11" s="4"/>
@@ -4145,7 +4163,9 @@
       <c r="BN12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO12" s="4"/>
+      <c r="BO12" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP12" s="4"/>
       <c r="BQ12" s="4"/>
       <c r="BR12" s="4"/>
@@ -4401,7 +4421,9 @@
       <c r="BN13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO13" s="4"/>
+      <c r="BO13" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP13" s="4"/>
       <c r="BQ13" s="4"/>
       <c r="BR13" s="4"/>
@@ -4657,7 +4679,9 @@
       <c r="BN14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO14" s="4"/>
+      <c r="BO14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP14" s="4"/>
       <c r="BQ14" s="4"/>
       <c r="BR14" s="4"/>
@@ -4913,7 +4937,9 @@
       <c r="BN15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO15" s="4"/>
+      <c r="BO15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP15" s="4"/>
       <c r="BQ15" s="4"/>
       <c r="BR15" s="4"/>
@@ -5169,7 +5195,9 @@
       <c r="BN16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO16" s="4"/>
+      <c r="BO16" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP16" s="4"/>
       <c r="BQ16" s="4"/>
       <c r="BR16" s="4"/>
@@ -5425,7 +5453,9 @@
       <c r="BN17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO17" s="4"/>
+      <c r="BO17" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP17" s="4"/>
       <c r="BQ17" s="4"/>
       <c r="BR17" s="4"/>
@@ -5681,7 +5711,9 @@
       <c r="BN18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO18" s="4"/>
+      <c r="BO18" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP18" s="4"/>
       <c r="BQ18" s="4"/>
       <c r="BR18" s="4"/>
@@ -5937,7 +5969,9 @@
       <c r="BN19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO19" s="4"/>
+      <c r="BO19" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP19" s="4"/>
       <c r="BQ19" s="4"/>
       <c r="BR19" s="4"/>
@@ -6193,7 +6227,9 @@
       <c r="BN20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO20" s="4"/>
+      <c r="BO20" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP20" s="4"/>
       <c r="BQ20" s="4"/>
       <c r="BR20" s="4"/>
@@ -6449,7 +6485,9 @@
       <c r="BN21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO21" s="4"/>
+      <c r="BO21" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP21" s="4"/>
       <c r="BQ21" s="4"/>
       <c r="BR21" s="4"/>
@@ -6705,7 +6743,9 @@
       <c r="BN22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO22" s="4"/>
+      <c r="BO22" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP22" s="4"/>
       <c r="BQ22" s="4"/>
       <c r="BR22" s="4"/>
@@ -6961,7 +7001,9 @@
       <c r="BN23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO23" s="4"/>
+      <c r="BO23" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP23" s="4"/>
       <c r="BQ23" s="4"/>
       <c r="BR23" s="4"/>
@@ -7217,7 +7259,9 @@
       <c r="BN24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO24" s="4"/>
+      <c r="BO24" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP24" s="4"/>
       <c r="BQ24" s="4"/>
       <c r="BR24" s="4"/>
@@ -7473,7 +7517,9 @@
       <c r="BN25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO25" s="4"/>
+      <c r="BO25" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP25" s="4"/>
       <c r="BQ25" s="4"/>
       <c r="BR25" s="4"/>
@@ -7729,7 +7775,9 @@
       <c r="BN26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO26" s="4"/>
+      <c r="BO26" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP26" s="4"/>
       <c r="BQ26" s="4"/>
       <c r="BR26" s="4"/>
@@ -7985,7 +8033,9 @@
       <c r="BN27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO27" s="4"/>
+      <c r="BO27" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP27" s="4"/>
       <c r="BQ27" s="4"/>
       <c r="BR27" s="4"/>
@@ -8241,7 +8291,9 @@
       <c r="BN28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO28" s="4"/>
+      <c r="BO28" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP28" s="4"/>
       <c r="BQ28" s="4"/>
       <c r="BR28" s="4"/>
@@ -8497,7 +8549,9 @@
       <c r="BN29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO29" s="4"/>
+      <c r="BO29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP29" s="4"/>
       <c r="BQ29" s="4"/>
       <c r="BR29" s="4"/>
@@ -8753,7 +8807,9 @@
       <c r="BN30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO30" s="4"/>
+      <c r="BO30" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP30" s="4"/>
       <c r="BQ30" s="4"/>
       <c r="BR30" s="4"/>
@@ -9009,7 +9065,9 @@
       <c r="BN31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BO31" s="4"/>
+      <c r="BO31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BP31" s="4"/>
       <c r="BQ31" s="4"/>
       <c r="BR31" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55EDA375-B9F0-4C8D-B291-CD5779F5BD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A213642-CD17-412C-808A-CCD17F11540B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -1388,8 +1388,12 @@
       <c r="BO1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BP1" s="7"/>
-      <c r="BQ1" s="7"/>
+      <c r="BP1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="BQ1" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="BR1" s="7"/>
       <c r="BS1" s="3"/>
       <c r="BT1" s="3"/>
@@ -1615,8 +1619,12 @@
       <c r="BO2" s="7">
         <v>46304</v>
       </c>
-      <c r="BP2" s="1"/>
-      <c r="BQ2" s="7"/>
+      <c r="BP2" s="1">
+        <v>46309</v>
+      </c>
+      <c r="BQ2" s="7">
+        <v>46311</v>
+      </c>
       <c r="BR2" s="1"/>
       <c r="BS2" s="4"/>
       <c r="BT2" s="4"/>
@@ -1841,7 +1849,9 @@
       <c r="BO3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP3" s="4"/>
+      <c r="BP3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ3" s="4"/>
       <c r="BR3" s="4"/>
       <c r="BS3" s="4"/>
@@ -2099,7 +2109,9 @@
       <c r="BO4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP4" s="4"/>
+      <c r="BP4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ4" s="4"/>
       <c r="BR4" s="4"/>
       <c r="BS4" s="4"/>
@@ -2357,7 +2369,9 @@
       <c r="BO5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP5" s="4"/>
+      <c r="BP5" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ5" s="4"/>
       <c r="BR5" s="4"/>
       <c r="BS5" s="4"/>
@@ -2615,7 +2629,9 @@
       <c r="BO6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP6" s="4"/>
+      <c r="BP6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ6" s="4"/>
       <c r="BR6" s="4"/>
       <c r="BS6" s="4"/>
@@ -2873,7 +2889,9 @@
       <c r="BO7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP7" s="4"/>
+      <c r="BP7" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ7" s="4"/>
       <c r="BR7" s="4"/>
       <c r="BS7" s="4"/>
@@ -3131,7 +3149,9 @@
       <c r="BO8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP8" s="4"/>
+      <c r="BP8" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ8" s="4"/>
       <c r="BR8" s="4"/>
       <c r="BS8" s="4"/>
@@ -3389,7 +3409,9 @@
       <c r="BO9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP9" s="4"/>
+      <c r="BP9" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ9" s="4"/>
       <c r="BR9" s="4"/>
       <c r="BS9" s="4"/>
@@ -3647,7 +3669,9 @@
       <c r="BO10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP10" s="4"/>
+      <c r="BP10" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ10" s="4"/>
       <c r="BR10" s="4"/>
       <c r="BS10" s="4"/>
@@ -3905,7 +3929,9 @@
       <c r="BO11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP11" s="4"/>
+      <c r="BP11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ11" s="4"/>
       <c r="BR11" s="4"/>
       <c r="BS11" s="4"/>
@@ -4166,7 +4192,9 @@
       <c r="BO12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP12" s="4"/>
+      <c r="BP12" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ12" s="4"/>
       <c r="BR12" s="4"/>
       <c r="BS12" s="4"/>
@@ -4424,7 +4452,9 @@
       <c r="BO13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP13" s="4"/>
+      <c r="BP13" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ13" s="4"/>
       <c r="BR13" s="4"/>
       <c r="BS13" s="4"/>
@@ -4682,7 +4712,9 @@
       <c r="BO14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP14" s="4"/>
+      <c r="BP14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ14" s="4"/>
       <c r="BR14" s="4"/>
       <c r="BS14" s="4"/>
@@ -4940,7 +4972,9 @@
       <c r="BO15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP15" s="4"/>
+      <c r="BP15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ15" s="4"/>
       <c r="BR15" s="4"/>
       <c r="BS15" s="4"/>
@@ -5198,7 +5232,9 @@
       <c r="BO16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP16" s="4"/>
+      <c r="BP16" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ16" s="4"/>
       <c r="BR16" s="4"/>
       <c r="BS16" s="4"/>
@@ -5456,7 +5492,9 @@
       <c r="BO17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP17" s="4"/>
+      <c r="BP17" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ17" s="4"/>
       <c r="BR17" s="4"/>
       <c r="BS17" s="4"/>
@@ -5714,7 +5752,9 @@
       <c r="BO18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP18" s="4"/>
+      <c r="BP18" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ18" s="4"/>
       <c r="BR18" s="4"/>
       <c r="BS18" s="4"/>
@@ -5972,7 +6012,9 @@
       <c r="BO19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP19" s="4"/>
+      <c r="BP19" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ19" s="4"/>
       <c r="BR19" s="4"/>
       <c r="BS19" s="4"/>
@@ -6230,7 +6272,9 @@
       <c r="BO20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP20" s="4"/>
+      <c r="BP20" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ20" s="4"/>
       <c r="BR20" s="4"/>
       <c r="BS20" s="4"/>
@@ -6488,7 +6532,9 @@
       <c r="BO21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP21" s="4"/>
+      <c r="BP21" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ21" s="4"/>
       <c r="BR21" s="4"/>
       <c r="BS21" s="4"/>
@@ -6746,7 +6792,9 @@
       <c r="BO22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP22" s="4"/>
+      <c r="BP22" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ22" s="4"/>
       <c r="BR22" s="4"/>
       <c r="BS22" s="4"/>
@@ -7004,7 +7052,9 @@
       <c r="BO23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP23" s="4"/>
+      <c r="BP23" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ23" s="4"/>
       <c r="BR23" s="4"/>
       <c r="BS23" s="4"/>
@@ -7262,7 +7312,9 @@
       <c r="BO24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP24" s="4"/>
+      <c r="BP24" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ24" s="4"/>
       <c r="BR24" s="4"/>
       <c r="BS24" s="4"/>
@@ -7520,7 +7572,9 @@
       <c r="BO25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP25" s="4"/>
+      <c r="BP25" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ25" s="4"/>
       <c r="BR25" s="4"/>
       <c r="BS25" s="4"/>
@@ -7778,7 +7832,9 @@
       <c r="BO26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP26" s="4"/>
+      <c r="BP26" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ26" s="4"/>
       <c r="BR26" s="4"/>
       <c r="BS26" s="4"/>
@@ -8036,7 +8092,9 @@
       <c r="BO27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP27" s="4"/>
+      <c r="BP27" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ27" s="4"/>
       <c r="BR27" s="4"/>
       <c r="BS27" s="4"/>
@@ -8294,7 +8352,9 @@
       <c r="BO28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP28" s="4"/>
+      <c r="BP28" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ28" s="4"/>
       <c r="BR28" s="4"/>
       <c r="BS28" s="4"/>
@@ -8552,7 +8612,9 @@
       <c r="BO29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP29" s="4"/>
+      <c r="BP29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ29" s="4"/>
       <c r="BR29" s="4"/>
       <c r="BS29" s="4"/>
@@ -8810,7 +8872,9 @@
       <c r="BO30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP30" s="4"/>
+      <c r="BP30" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ30" s="4"/>
       <c r="BR30" s="4"/>
       <c r="BS30" s="4"/>
@@ -9068,7 +9132,9 @@
       <c r="BO31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BP31" s="4"/>
+      <c r="BP31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BQ31" s="4"/>
       <c r="BR31" s="4"/>
       <c r="BS31" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A213642-CD17-412C-808A-CCD17F11540B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFB1CAB-3FD8-4D45-ADAD-7F31246E3872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -1175,24 +1175,26 @@
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="106" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="7" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="50" width="7" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="55" width="7" bestFit="1" customWidth="1"/>
+    <col min="56" max="64" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="65" max="69" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="70" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:123" x14ac:dyDescent="0.25">
@@ -1394,8 +1396,12 @@
       <c r="BQ1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BR1" s="7"/>
-      <c r="BS1" s="3"/>
+      <c r="BR1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS1" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="BT1" s="3"/>
       <c r="BU1" s="3"/>
       <c r="BV1" s="3"/>
@@ -1852,7 +1858,9 @@
       <c r="BP3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ3" s="4"/>
+      <c r="BQ3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR3" s="4"/>
       <c r="BS3" s="4"/>
       <c r="BT3" s="4"/>
@@ -2112,7 +2120,9 @@
       <c r="BP4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ4" s="4"/>
+      <c r="BQ4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR4" s="4"/>
       <c r="BS4" s="4"/>
       <c r="BT4" s="4"/>
@@ -2372,7 +2382,9 @@
       <c r="BP5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ5" s="4"/>
+      <c r="BQ5" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR5" s="4"/>
       <c r="BS5" s="4"/>
       <c r="BT5" s="4"/>
@@ -2632,7 +2644,9 @@
       <c r="BP6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ6" s="4"/>
+      <c r="BQ6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR6" s="4"/>
       <c r="BS6" s="4"/>
       <c r="BT6" s="4"/>
@@ -2892,7 +2906,9 @@
       <c r="BP7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ7" s="4"/>
+      <c r="BQ7" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR7" s="4"/>
       <c r="BS7" s="4"/>
       <c r="BT7" s="4"/>
@@ -3152,7 +3168,9 @@
       <c r="BP8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ8" s="4"/>
+      <c r="BQ8" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR8" s="4"/>
       <c r="BS8" s="4"/>
       <c r="BT8" s="4"/>
@@ -3412,7 +3430,9 @@
       <c r="BP9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ9" s="4"/>
+      <c r="BQ9" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR9" s="4"/>
       <c r="BS9" s="4"/>
       <c r="BT9" s="4"/>
@@ -3672,7 +3692,9 @@
       <c r="BP10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ10" s="4"/>
+      <c r="BQ10" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR10" s="4"/>
       <c r="BS10" s="4"/>
       <c r="BT10" s="4"/>
@@ -3932,7 +3954,9 @@
       <c r="BP11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ11" s="4"/>
+      <c r="BQ11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR11" s="4"/>
       <c r="BS11" s="4"/>
       <c r="BT11" s="4"/>
@@ -4195,7 +4219,9 @@
       <c r="BP12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ12" s="4"/>
+      <c r="BQ12" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR12" s="4"/>
       <c r="BS12" s="4"/>
       <c r="BT12" s="4"/>
@@ -4455,7 +4481,9 @@
       <c r="BP13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ13" s="4"/>
+      <c r="BQ13" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR13" s="4"/>
       <c r="BS13" s="4"/>
       <c r="BT13" s="4"/>
@@ -4715,7 +4743,9 @@
       <c r="BP14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ14" s="4"/>
+      <c r="BQ14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR14" s="4"/>
       <c r="BS14" s="4"/>
       <c r="BT14" s="4"/>
@@ -4975,7 +5005,9 @@
       <c r="BP15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ15" s="4"/>
+      <c r="BQ15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR15" s="4"/>
       <c r="BS15" s="4"/>
       <c r="BT15" s="4"/>
@@ -5235,7 +5267,9 @@
       <c r="BP16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ16" s="4"/>
+      <c r="BQ16" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR16" s="4"/>
       <c r="BS16" s="4"/>
       <c r="BT16" s="4"/>
@@ -5495,7 +5529,9 @@
       <c r="BP17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ17" s="4"/>
+      <c r="BQ17" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR17" s="4"/>
       <c r="BS17" s="4"/>
       <c r="BT17" s="4"/>
@@ -5755,7 +5791,9 @@
       <c r="BP18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ18" s="4"/>
+      <c r="BQ18" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR18" s="4"/>
       <c r="BS18" s="4"/>
       <c r="BT18" s="4"/>
@@ -6015,7 +6053,9 @@
       <c r="BP19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ19" s="4"/>
+      <c r="BQ19" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR19" s="4"/>
       <c r="BS19" s="4"/>
       <c r="BT19" s="4"/>
@@ -6275,7 +6315,9 @@
       <c r="BP20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ20" s="4"/>
+      <c r="BQ20" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR20" s="4"/>
       <c r="BS20" s="4"/>
       <c r="BT20" s="4"/>
@@ -6535,7 +6577,9 @@
       <c r="BP21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ21" s="4"/>
+      <c r="BQ21" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR21" s="4"/>
       <c r="BS21" s="4"/>
       <c r="BT21" s="4"/>
@@ -6795,7 +6839,9 @@
       <c r="BP22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ22" s="4"/>
+      <c r="BQ22" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR22" s="4"/>
       <c r="BS22" s="4"/>
       <c r="BT22" s="4"/>
@@ -7055,7 +7101,9 @@
       <c r="BP23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ23" s="4"/>
+      <c r="BQ23" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR23" s="4"/>
       <c r="BS23" s="4"/>
       <c r="BT23" s="4"/>
@@ -7315,7 +7363,9 @@
       <c r="BP24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ24" s="4"/>
+      <c r="BQ24" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR24" s="4"/>
       <c r="BS24" s="4"/>
       <c r="BT24" s="4"/>
@@ -7575,7 +7625,9 @@
       <c r="BP25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ25" s="4"/>
+      <c r="BQ25" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR25" s="4"/>
       <c r="BS25" s="4"/>
       <c r="BT25" s="4"/>
@@ -7835,7 +7887,9 @@
       <c r="BP26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ26" s="4"/>
+      <c r="BQ26" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR26" s="4"/>
       <c r="BS26" s="4"/>
       <c r="BT26" s="4"/>
@@ -8095,7 +8149,9 @@
       <c r="BP27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ27" s="4"/>
+      <c r="BQ27" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR27" s="4"/>
       <c r="BS27" s="4"/>
       <c r="BT27" s="4"/>
@@ -8355,7 +8411,9 @@
       <c r="BP28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ28" s="4"/>
+      <c r="BQ28" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR28" s="4"/>
       <c r="BS28" s="4"/>
       <c r="BT28" s="4"/>
@@ -8615,7 +8673,9 @@
       <c r="BP29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ29" s="4"/>
+      <c r="BQ29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR29" s="4"/>
       <c r="BS29" s="4"/>
       <c r="BT29" s="4"/>
@@ -8875,7 +8935,9 @@
       <c r="BP30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ30" s="4"/>
+      <c r="BQ30" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR30" s="4"/>
       <c r="BS30" s="4"/>
       <c r="BT30" s="4"/>
@@ -9135,7 +9197,9 @@
       <c r="BP31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ31" s="4"/>
+      <c r="BQ31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BR31" s="4"/>
       <c r="BS31" s="4"/>
       <c r="BT31" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFB1CAB-3FD8-4D45-ADAD-7F31246E3872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E91AB5-ED16-414B-A19C-4249B9488688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -713,7 +713,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -726,6 +726,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1396,7 +1399,7 @@
       <c r="BQ1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BR1" s="7" t="s">
+      <c r="BR1" s="10" t="s">
         <v>31</v>
       </c>
       <c r="BS1" s="7" t="s">
@@ -1631,7 +1634,9 @@
       <c r="BQ2" s="7">
         <v>46311</v>
       </c>
-      <c r="BR2" s="1"/>
+      <c r="BR2" s="1">
+        <v>46316</v>
+      </c>
       <c r="BS2" s="4"/>
       <c r="BT2" s="4"/>
       <c r="BU2" s="4"/>
@@ -1861,7 +1866,9 @@
       <c r="BQ3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR3" s="4"/>
+      <c r="BR3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS3" s="4"/>
       <c r="BT3" s="4"/>
       <c r="BU3" s="4"/>
@@ -2123,7 +2130,9 @@
       <c r="BQ4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR4" s="4"/>
+      <c r="BR4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS4" s="4"/>
       <c r="BT4" s="4"/>
       <c r="BU4" s="4"/>
@@ -2385,7 +2394,9 @@
       <c r="BQ5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR5" s="4"/>
+      <c r="BR5" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS5" s="4"/>
       <c r="BT5" s="4"/>
       <c r="BU5" s="4"/>
@@ -2647,7 +2658,9 @@
       <c r="BQ6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR6" s="4"/>
+      <c r="BR6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS6" s="4"/>
       <c r="BT6" s="4"/>
       <c r="BU6" s="4"/>
@@ -2909,7 +2922,9 @@
       <c r="BQ7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR7" s="4"/>
+      <c r="BR7" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS7" s="4"/>
       <c r="BT7" s="4"/>
       <c r="BU7" s="4"/>
@@ -3171,7 +3186,9 @@
       <c r="BQ8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR8" s="4"/>
+      <c r="BR8" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS8" s="4"/>
       <c r="BT8" s="4"/>
       <c r="BU8" s="4"/>
@@ -3433,7 +3450,9 @@
       <c r="BQ9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR9" s="4"/>
+      <c r="BR9" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS9" s="4"/>
       <c r="BT9" s="4"/>
       <c r="BU9" s="4"/>
@@ -3695,7 +3714,9 @@
       <c r="BQ10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR10" s="4"/>
+      <c r="BR10" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS10" s="4"/>
       <c r="BT10" s="4"/>
       <c r="BU10" s="4"/>
@@ -3957,7 +3978,9 @@
       <c r="BQ11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR11" s="4"/>
+      <c r="BR11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS11" s="4"/>
       <c r="BT11" s="4"/>
       <c r="BU11" s="4"/>
@@ -4222,7 +4245,9 @@
       <c r="BQ12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR12" s="4"/>
+      <c r="BR12" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS12" s="4"/>
       <c r="BT12" s="4"/>
       <c r="BU12" s="4"/>
@@ -4484,7 +4509,9 @@
       <c r="BQ13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR13" s="4"/>
+      <c r="BR13" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS13" s="4"/>
       <c r="BT13" s="4"/>
       <c r="BU13" s="4"/>
@@ -4746,7 +4773,9 @@
       <c r="BQ14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR14" s="4"/>
+      <c r="BR14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS14" s="4"/>
       <c r="BT14" s="4"/>
       <c r="BU14" s="4"/>
@@ -5008,7 +5037,9 @@
       <c r="BQ15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR15" s="4"/>
+      <c r="BR15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS15" s="4"/>
       <c r="BT15" s="4"/>
       <c r="BU15" s="4"/>
@@ -5270,7 +5301,9 @@
       <c r="BQ16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR16" s="4"/>
+      <c r="BR16" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS16" s="4"/>
       <c r="BT16" s="4"/>
       <c r="BU16" s="4"/>
@@ -5532,7 +5565,9 @@
       <c r="BQ17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR17" s="4"/>
+      <c r="BR17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BS17" s="4"/>
       <c r="BT17" s="4"/>
       <c r="BU17" s="4"/>
@@ -5794,7 +5829,9 @@
       <c r="BQ18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR18" s="4"/>
+      <c r="BR18" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS18" s="4"/>
       <c r="BT18" s="4"/>
       <c r="BU18" s="4"/>
@@ -6056,7 +6093,9 @@
       <c r="BQ19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR19" s="4"/>
+      <c r="BR19" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS19" s="4"/>
       <c r="BT19" s="4"/>
       <c r="BU19" s="4"/>
@@ -6318,7 +6357,9 @@
       <c r="BQ20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR20" s="4"/>
+      <c r="BR20" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS20" s="4"/>
       <c r="BT20" s="4"/>
       <c r="BU20" s="4"/>
@@ -6580,7 +6621,9 @@
       <c r="BQ21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR21" s="4"/>
+      <c r="BR21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BS21" s="4"/>
       <c r="BT21" s="4"/>
       <c r="BU21" s="4"/>
@@ -6842,7 +6885,9 @@
       <c r="BQ22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR22" s="4"/>
+      <c r="BR22" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="BS22" s="4"/>
       <c r="BT22" s="4"/>
       <c r="BU22" s="4"/>
@@ -7104,7 +7149,9 @@
       <c r="BQ23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR23" s="4"/>
+      <c r="BR23" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS23" s="4"/>
       <c r="BT23" s="4"/>
       <c r="BU23" s="4"/>
@@ -7366,7 +7413,9 @@
       <c r="BQ24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR24" s="4"/>
+      <c r="BR24" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS24" s="4"/>
       <c r="BT24" s="4"/>
       <c r="BU24" s="4"/>
@@ -7628,7 +7677,9 @@
       <c r="BQ25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR25" s="4"/>
+      <c r="BR25" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS25" s="4"/>
       <c r="BT25" s="4"/>
       <c r="BU25" s="4"/>
@@ -7890,7 +7941,9 @@
       <c r="BQ26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR26" s="4"/>
+      <c r="BR26" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS26" s="4"/>
       <c r="BT26" s="4"/>
       <c r="BU26" s="4"/>
@@ -8152,7 +8205,9 @@
       <c r="BQ27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR27" s="4"/>
+      <c r="BR27" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS27" s="4"/>
       <c r="BT27" s="4"/>
       <c r="BU27" s="4"/>
@@ -8414,7 +8469,9 @@
       <c r="BQ28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR28" s="4"/>
+      <c r="BR28" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS28" s="4"/>
       <c r="BT28" s="4"/>
       <c r="BU28" s="4"/>
@@ -8676,7 +8733,9 @@
       <c r="BQ29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR29" s="4"/>
+      <c r="BR29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS29" s="4"/>
       <c r="BT29" s="4"/>
       <c r="BU29" s="4"/>
@@ -8938,7 +8997,9 @@
       <c r="BQ30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR30" s="4"/>
+      <c r="BR30" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS30" s="4"/>
       <c r="BT30" s="4"/>
       <c r="BU30" s="4"/>
@@ -9200,7 +9261,9 @@
       <c r="BQ31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BR31" s="4"/>
+      <c r="BR31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BS31" s="4"/>
       <c r="BT31" s="4"/>
       <c r="BU31" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E91AB5-ED16-414B-A19C-4249B9488688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804931DE-28DA-471E-BA32-7094DE1DD27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -713,7 +713,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -726,9 +726,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1399,7 +1396,7 @@
       <c r="BQ1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BR1" s="10" t="s">
+      <c r="BR1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="BS1" s="7" t="s">
@@ -1637,7 +1634,9 @@
       <c r="BR2" s="1">
         <v>46316</v>
       </c>
-      <c r="BS2" s="4"/>
+      <c r="BS2" s="1">
+        <v>46318</v>
+      </c>
       <c r="BT2" s="4"/>
       <c r="BU2" s="4"/>
       <c r="BV2" s="4"/>
@@ -1869,7 +1868,9 @@
       <c r="BR3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS3" s="4"/>
+      <c r="BS3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT3" s="4"/>
       <c r="BU3" s="4"/>
       <c r="BV3" s="4"/>
@@ -2133,7 +2134,9 @@
       <c r="BR4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS4" s="4"/>
+      <c r="BS4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT4" s="4"/>
       <c r="BU4" s="4"/>
       <c r="BV4" s="4"/>
@@ -2397,7 +2400,9 @@
       <c r="BR5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS5" s="4"/>
+      <c r="BS5" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT5" s="4"/>
       <c r="BU5" s="4"/>
       <c r="BV5" s="4"/>
@@ -2661,7 +2666,9 @@
       <c r="BR6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS6" s="4"/>
+      <c r="BS6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT6" s="4"/>
       <c r="BU6" s="4"/>
       <c r="BV6" s="4"/>
@@ -2925,7 +2932,9 @@
       <c r="BR7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS7" s="4"/>
+      <c r="BS7" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT7" s="4"/>
       <c r="BU7" s="4"/>
       <c r="BV7" s="4"/>
@@ -3189,7 +3198,9 @@
       <c r="BR8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS8" s="4"/>
+      <c r="BS8" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT8" s="4"/>
       <c r="BU8" s="4"/>
       <c r="BV8" s="4"/>
@@ -3453,7 +3464,9 @@
       <c r="BR9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS9" s="4"/>
+      <c r="BS9" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT9" s="4"/>
       <c r="BU9" s="4"/>
       <c r="BV9" s="4"/>
@@ -3717,7 +3730,9 @@
       <c r="BR10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS10" s="4"/>
+      <c r="BS10" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT10" s="4"/>
       <c r="BU10" s="4"/>
       <c r="BV10" s="4"/>
@@ -3981,7 +3996,9 @@
       <c r="BR11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS11" s="4"/>
+      <c r="BS11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT11" s="4"/>
       <c r="BU11" s="4"/>
       <c r="BV11" s="4"/>
@@ -4248,7 +4265,9 @@
       <c r="BR12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS12" s="4"/>
+      <c r="BS12" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT12" s="4"/>
       <c r="BU12" s="4"/>
       <c r="BV12" s="4"/>
@@ -4512,7 +4531,9 @@
       <c r="BR13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS13" s="4"/>
+      <c r="BS13" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT13" s="4"/>
       <c r="BU13" s="4"/>
       <c r="BV13" s="4"/>
@@ -4776,7 +4797,9 @@
       <c r="BR14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS14" s="4"/>
+      <c r="BS14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT14" s="4"/>
       <c r="BU14" s="4"/>
       <c r="BV14" s="4"/>
@@ -5040,7 +5063,9 @@
       <c r="BR15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS15" s="4"/>
+      <c r="BS15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT15" s="4"/>
       <c r="BU15" s="4"/>
       <c r="BV15" s="4"/>
@@ -5304,7 +5329,9 @@
       <c r="BR16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS16" s="4"/>
+      <c r="BS16" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT16" s="4"/>
       <c r="BU16" s="4"/>
       <c r="BV16" s="4"/>
@@ -5568,7 +5595,9 @@
       <c r="BR17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BS17" s="4"/>
+      <c r="BS17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BT17" s="4"/>
       <c r="BU17" s="4"/>
       <c r="BV17" s="4"/>
@@ -5832,7 +5861,9 @@
       <c r="BR18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS18" s="4"/>
+      <c r="BS18" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT18" s="4"/>
       <c r="BU18" s="4"/>
       <c r="BV18" s="4"/>
@@ -6096,7 +6127,9 @@
       <c r="BR19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS19" s="4"/>
+      <c r="BS19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BT19" s="4"/>
       <c r="BU19" s="4"/>
       <c r="BV19" s="4"/>
@@ -6360,7 +6393,9 @@
       <c r="BR20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS20" s="4"/>
+      <c r="BS20" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT20" s="4"/>
       <c r="BU20" s="4"/>
       <c r="BV20" s="4"/>
@@ -6624,7 +6659,9 @@
       <c r="BR21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BS21" s="4"/>
+      <c r="BS21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BT21" s="4"/>
       <c r="BU21" s="4"/>
       <c r="BV21" s="4"/>
@@ -6888,7 +6925,9 @@
       <c r="BR22" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="BS22" s="4"/>
+      <c r="BS22" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT22" s="4"/>
       <c r="BU22" s="4"/>
       <c r="BV22" s="4"/>
@@ -7152,7 +7191,9 @@
       <c r="BR23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS23" s="4"/>
+      <c r="BS23" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT23" s="4"/>
       <c r="BU23" s="4"/>
       <c r="BV23" s="4"/>
@@ -7416,7 +7457,9 @@
       <c r="BR24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS24" s="4"/>
+      <c r="BS24" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT24" s="4"/>
       <c r="BU24" s="4"/>
       <c r="BV24" s="4"/>
@@ -7680,7 +7723,9 @@
       <c r="BR25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS25" s="4"/>
+      <c r="BS25" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT25" s="4"/>
       <c r="BU25" s="4"/>
       <c r="BV25" s="4"/>
@@ -7944,7 +7989,9 @@
       <c r="BR26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS26" s="4"/>
+      <c r="BS26" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT26" s="4"/>
       <c r="BU26" s="4"/>
       <c r="BV26" s="4"/>
@@ -8208,7 +8255,9 @@
       <c r="BR27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS27" s="4"/>
+      <c r="BS27" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT27" s="4"/>
       <c r="BU27" s="4"/>
       <c r="BV27" s="4"/>
@@ -8472,7 +8521,9 @@
       <c r="BR28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS28" s="4"/>
+      <c r="BS28" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT28" s="4"/>
       <c r="BU28" s="4"/>
       <c r="BV28" s="4"/>
@@ -8736,7 +8787,9 @@
       <c r="BR29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS29" s="4"/>
+      <c r="BS29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT29" s="4"/>
       <c r="BU29" s="4"/>
       <c r="BV29" s="4"/>
@@ -9000,7 +9053,9 @@
       <c r="BR30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS30" s="4"/>
+      <c r="BS30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BT30" s="4"/>
       <c r="BU30" s="4"/>
       <c r="BV30" s="4"/>
@@ -9264,7 +9319,9 @@
       <c r="BR31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BS31" s="4"/>
+      <c r="BS31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BT31" s="4"/>
       <c r="BU31" s="4"/>
       <c r="BV31" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804931DE-28DA-471E-BA32-7094DE1DD27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FEDC87-2DBA-49E7-8330-E49479049BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6660,7 +6660,7 @@
         <v>34</v>
       </c>
       <c r="BS21" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="BT21" s="4"/>
       <c r="BU21" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FEDC87-2DBA-49E7-8330-E49479049BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66C1DA3-B703-43BF-8A5C-5F6261C5DF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -774,7 +774,17 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -9054,7 +9064,7 @@
         <v>33</v>
       </c>
       <c r="BS30" s="4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BT30" s="4"/>
       <c r="BU30" s="4"/>
@@ -9383,64 +9393,69 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB25">
     <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="BE3:BE31">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG3:BG31">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BG3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI7">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI12">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI20">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM1:BM1048576">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BM1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN3:BN31">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BN3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BS30">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BN3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BS30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66C1DA3-B703-43BF-8A5C-5F6261C5DF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B38481-C416-4584-8F76-3332C8ABC82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -1412,7 +1412,9 @@
       <c r="BS1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BT1" s="3"/>
+      <c r="BT1" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU1" s="3"/>
       <c r="BV1" s="3"/>
       <c r="BW1" s="3"/>
@@ -1647,7 +1649,9 @@
       <c r="BS2" s="1">
         <v>46318</v>
       </c>
-      <c r="BT2" s="4"/>
+      <c r="BT2" s="3">
+        <v>46323</v>
+      </c>
       <c r="BU2" s="4"/>
       <c r="BV2" s="4"/>
       <c r="BW2" s="4"/>
@@ -1881,7 +1885,9 @@
       <c r="BS3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT3" s="4"/>
+      <c r="BT3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU3" s="4"/>
       <c r="BV3" s="4"/>
       <c r="BW3" s="4"/>
@@ -2147,7 +2153,9 @@
       <c r="BS4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT4" s="4"/>
+      <c r="BT4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU4" s="4"/>
       <c r="BV4" s="4"/>
       <c r="BW4" s="4"/>
@@ -2413,7 +2421,9 @@
       <c r="BS5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT5" s="4"/>
+      <c r="BT5" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU5" s="4"/>
       <c r="BV5" s="4"/>
       <c r="BW5" s="4"/>
@@ -2679,7 +2689,9 @@
       <c r="BS6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT6" s="4"/>
+      <c r="BT6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU6" s="4"/>
       <c r="BV6" s="4"/>
       <c r="BW6" s="4"/>
@@ -2945,7 +2957,9 @@
       <c r="BS7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT7" s="4"/>
+      <c r="BT7" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU7" s="4"/>
       <c r="BV7" s="4"/>
       <c r="BW7" s="4"/>
@@ -3211,7 +3225,9 @@
       <c r="BS8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT8" s="4"/>
+      <c r="BT8" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU8" s="4"/>
       <c r="BV8" s="4"/>
       <c r="BW8" s="4"/>
@@ -3477,7 +3493,9 @@
       <c r="BS9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT9" s="4"/>
+      <c r="BT9" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU9" s="4"/>
       <c r="BV9" s="4"/>
       <c r="BW9" s="4"/>
@@ -3743,7 +3761,9 @@
       <c r="BS10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT10" s="4"/>
+      <c r="BT10" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU10" s="4"/>
       <c r="BV10" s="4"/>
       <c r="BW10" s="4"/>
@@ -4009,7 +4029,9 @@
       <c r="BS11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT11" s="4"/>
+      <c r="BT11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU11" s="4"/>
       <c r="BV11" s="4"/>
       <c r="BW11" s="4"/>
@@ -4278,7 +4300,9 @@
       <c r="BS12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT12" s="4"/>
+      <c r="BT12" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU12" s="4"/>
       <c r="BV12" s="4"/>
       <c r="BW12" s="4"/>
@@ -4544,7 +4568,9 @@
       <c r="BS13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT13" s="4"/>
+      <c r="BT13" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU13" s="4"/>
       <c r="BV13" s="4"/>
       <c r="BW13" s="4"/>
@@ -4810,7 +4836,9 @@
       <c r="BS14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT14" s="4"/>
+      <c r="BT14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU14" s="4"/>
       <c r="BV14" s="4"/>
       <c r="BW14" s="4"/>
@@ -5076,7 +5104,9 @@
       <c r="BS15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT15" s="4"/>
+      <c r="BT15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU15" s="4"/>
       <c r="BV15" s="4"/>
       <c r="BW15" s="4"/>
@@ -5342,7 +5372,9 @@
       <c r="BS16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT16" s="4"/>
+      <c r="BT16" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU16" s="4"/>
       <c r="BV16" s="4"/>
       <c r="BW16" s="4"/>
@@ -5608,7 +5640,9 @@
       <c r="BS17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BT17" s="4"/>
+      <c r="BT17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BU17" s="4"/>
       <c r="BV17" s="4"/>
       <c r="BW17" s="4"/>
@@ -5874,7 +5908,9 @@
       <c r="BS18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT18" s="4"/>
+      <c r="BT18" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU18" s="4"/>
       <c r="BV18" s="4"/>
       <c r="BW18" s="4"/>
@@ -6140,7 +6176,9 @@
       <c r="BS19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BT19" s="4"/>
+      <c r="BT19" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU19" s="4"/>
       <c r="BV19" s="4"/>
       <c r="BW19" s="4"/>
@@ -6406,7 +6444,9 @@
       <c r="BS20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT20" s="4"/>
+      <c r="BT20" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU20" s="4"/>
       <c r="BV20" s="4"/>
       <c r="BW20" s="4"/>
@@ -6672,7 +6712,9 @@
       <c r="BS21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT21" s="4"/>
+      <c r="BT21" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU21" s="4"/>
       <c r="BV21" s="4"/>
       <c r="BW21" s="4"/>
@@ -6938,7 +6980,9 @@
       <c r="BS22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT22" s="4"/>
+      <c r="BT22" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU22" s="4"/>
       <c r="BV22" s="4"/>
       <c r="BW22" s="4"/>
@@ -7204,7 +7248,9 @@
       <c r="BS23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT23" s="4"/>
+      <c r="BT23" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU23" s="4"/>
       <c r="BV23" s="4"/>
       <c r="BW23" s="4"/>
@@ -7470,7 +7516,9 @@
       <c r="BS24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT24" s="4"/>
+      <c r="BT24" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU24" s="4"/>
       <c r="BV24" s="4"/>
       <c r="BW24" s="4"/>
@@ -7736,7 +7784,9 @@
       <c r="BS25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT25" s="4"/>
+      <c r="BT25" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU25" s="4"/>
       <c r="BV25" s="4"/>
       <c r="BW25" s="4"/>
@@ -8002,7 +8052,9 @@
       <c r="BS26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT26" s="4"/>
+      <c r="BT26" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU26" s="4"/>
       <c r="BV26" s="4"/>
       <c r="BW26" s="4"/>
@@ -8268,7 +8320,9 @@
       <c r="BS27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT27" s="4"/>
+      <c r="BT27" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU27" s="4"/>
       <c r="BV27" s="4"/>
       <c r="BW27" s="4"/>
@@ -8534,7 +8588,9 @@
       <c r="BS28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT28" s="4"/>
+      <c r="BT28" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU28" s="4"/>
       <c r="BV28" s="4"/>
       <c r="BW28" s="4"/>
@@ -8800,7 +8856,9 @@
       <c r="BS29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT29" s="4"/>
+      <c r="BT29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU29" s="4"/>
       <c r="BV29" s="4"/>
       <c r="BW29" s="4"/>
@@ -9066,7 +9124,9 @@
       <c r="BS30" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="BT30" s="4"/>
+      <c r="BT30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BU30" s="4"/>
       <c r="BV30" s="4"/>
       <c r="BW30" s="4"/>
@@ -9332,7 +9392,9 @@
       <c r="BS31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BT31" s="4"/>
+      <c r="BT31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BU31" s="4"/>
       <c r="BV31" s="4"/>
       <c r="BW31" s="4"/>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B38481-C416-4584-8F76-3332C8ABC82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4192EE7C-DEB1-4267-8735-23A65911B743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -1415,7 +1415,9 @@
       <c r="BT1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BU1" s="3"/>
+      <c r="BU1" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BV1" s="3"/>
       <c r="BW1" s="3"/>
       <c r="BX1" s="3"/>
@@ -1652,7 +1654,9 @@
       <c r="BT2" s="3">
         <v>46323</v>
       </c>
-      <c r="BU2" s="4"/>
+      <c r="BU2" s="3">
+        <v>46325</v>
+      </c>
       <c r="BV2" s="4"/>
       <c r="BW2" s="4"/>
       <c r="BX2" s="4"/>
@@ -1888,7 +1892,9 @@
       <c r="BT3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU3" s="4"/>
+      <c r="BU3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV3" s="4"/>
       <c r="BW3" s="4"/>
       <c r="BX3" s="4"/>
@@ -2156,7 +2162,9 @@
       <c r="BT4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU4" s="4"/>
+      <c r="BU4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV4" s="4"/>
       <c r="BW4" s="4"/>
       <c r="BX4" s="4"/>
@@ -2424,7 +2432,9 @@
       <c r="BT5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU5" s="4"/>
+      <c r="BU5" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV5" s="4"/>
       <c r="BW5" s="4"/>
       <c r="BX5" s="4"/>
@@ -2692,7 +2702,9 @@
       <c r="BT6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU6" s="4"/>
+      <c r="BU6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV6" s="4"/>
       <c r="BW6" s="4"/>
       <c r="BX6" s="4"/>
@@ -2960,7 +2972,9 @@
       <c r="BT7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU7" s="4"/>
+      <c r="BU7" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV7" s="4"/>
       <c r="BW7" s="4"/>
       <c r="BX7" s="4"/>
@@ -3228,7 +3242,9 @@
       <c r="BT8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU8" s="4"/>
+      <c r="BU8" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV8" s="4"/>
       <c r="BW8" s="4"/>
       <c r="BX8" s="4"/>
@@ -3496,7 +3512,9 @@
       <c r="BT9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU9" s="4"/>
+      <c r="BU9" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV9" s="4"/>
       <c r="BW9" s="4"/>
       <c r="BX9" s="4"/>
@@ -3764,7 +3782,9 @@
       <c r="BT10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU10" s="4"/>
+      <c r="BU10" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV10" s="4"/>
       <c r="BW10" s="4"/>
       <c r="BX10" s="4"/>
@@ -4032,7 +4052,9 @@
       <c r="BT11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU11" s="4"/>
+      <c r="BU11" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV11" s="4"/>
       <c r="BW11" s="4"/>
       <c r="BX11" s="4"/>
@@ -4303,7 +4325,9 @@
       <c r="BT12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU12" s="4"/>
+      <c r="BU12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="BV12" s="4"/>
       <c r="BW12" s="4"/>
       <c r="BX12" s="4"/>
@@ -4571,7 +4595,9 @@
       <c r="BT13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU13" s="4"/>
+      <c r="BU13" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV13" s="4"/>
       <c r="BW13" s="4"/>
       <c r="BX13" s="4"/>
@@ -4839,7 +4865,9 @@
       <c r="BT14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU14" s="4"/>
+      <c r="BU14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV14" s="4"/>
       <c r="BW14" s="4"/>
       <c r="BX14" s="4"/>
@@ -5107,7 +5135,9 @@
       <c r="BT15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU15" s="4"/>
+      <c r="BU15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV15" s="4"/>
       <c r="BW15" s="4"/>
       <c r="BX15" s="4"/>
@@ -5375,7 +5405,9 @@
       <c r="BT16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU16" s="4"/>
+      <c r="BU16" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV16" s="4"/>
       <c r="BW16" s="4"/>
       <c r="BX16" s="4"/>
@@ -5643,7 +5675,9 @@
       <c r="BT17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BU17" s="4"/>
+      <c r="BU17" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV17" s="4"/>
       <c r="BW17" s="4"/>
       <c r="BX17" s="4"/>
@@ -5911,7 +5945,9 @@
       <c r="BT18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU18" s="4"/>
+      <c r="BU18" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV18" s="4"/>
       <c r="BW18" s="4"/>
       <c r="BX18" s="4"/>
@@ -6179,7 +6215,9 @@
       <c r="BT19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU19" s="4"/>
+      <c r="BU19" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV19" s="4"/>
       <c r="BW19" s="4"/>
       <c r="BX19" s="4"/>
@@ -6447,7 +6485,9 @@
       <c r="BT20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU20" s="4"/>
+      <c r="BU20" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV20" s="4"/>
       <c r="BW20" s="4"/>
       <c r="BX20" s="4"/>
@@ -6715,7 +6755,9 @@
       <c r="BT21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU21" s="4"/>
+      <c r="BU21" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV21" s="4"/>
       <c r="BW21" s="4"/>
       <c r="BX21" s="4"/>
@@ -6983,7 +7025,9 @@
       <c r="BT22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU22" s="4"/>
+      <c r="BU22" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV22" s="4"/>
       <c r="BW22" s="4"/>
       <c r="BX22" s="4"/>
@@ -7251,7 +7295,9 @@
       <c r="BT23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU23" s="4"/>
+      <c r="BU23" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV23" s="4"/>
       <c r="BW23" s="4"/>
       <c r="BX23" s="4"/>
@@ -7519,7 +7565,9 @@
       <c r="BT24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU24" s="4"/>
+      <c r="BU24" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV24" s="4"/>
       <c r="BW24" s="4"/>
       <c r="BX24" s="4"/>
@@ -7787,7 +7835,9 @@
       <c r="BT25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU25" s="4"/>
+      <c r="BU25" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV25" s="4"/>
       <c r="BW25" s="4"/>
       <c r="BX25" s="4"/>
@@ -8055,7 +8105,9 @@
       <c r="BT26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU26" s="4"/>
+      <c r="BU26" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV26" s="4"/>
       <c r="BW26" s="4"/>
       <c r="BX26" s="4"/>
@@ -8323,7 +8375,9 @@
       <c r="BT27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU27" s="4"/>
+      <c r="BU27" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV27" s="4"/>
       <c r="BW27" s="4"/>
       <c r="BX27" s="4"/>
@@ -8591,7 +8645,9 @@
       <c r="BT28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU28" s="4"/>
+      <c r="BU28" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV28" s="4"/>
       <c r="BW28" s="4"/>
       <c r="BX28" s="4"/>
@@ -8859,7 +8915,9 @@
       <c r="BT29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU29" s="4"/>
+      <c r="BU29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV29" s="4"/>
       <c r="BW29" s="4"/>
       <c r="BX29" s="4"/>
@@ -9127,7 +9185,9 @@
       <c r="BT30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BU30" s="4"/>
+      <c r="BU30" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV30" s="4"/>
       <c r="BW30" s="4"/>
       <c r="BX30" s="4"/>
@@ -9395,7 +9455,9 @@
       <c r="BT31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BU31" s="4"/>
+      <c r="BU31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="BV31" s="4"/>
       <c r="BW31" s="4"/>
       <c r="BX31" s="4"/>
@@ -9455,7 +9517,7 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
     <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_A/frequencia-3-A.xlsx
+++ b/ds/turmas/2DES_A/frequencia-3-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\2DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4192EE7C-DEB1-4267-8735-23A65911B743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD666698-D516-417E-9B14-65660A04C280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -774,7 +774,57 @@
     <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3243,7 +3293,7 @@
         <v>33</v>
       </c>
       <c r="BU8" s="4" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="BV8" s="4"/>
       <c r="BW8" s="4"/>
@@ -4326,7 +4376,7 @@
         <v>33</v>
       </c>
       <c r="BU12" s="4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BV12" s="4"/>
       <c r="BW12" s="4"/>
@@ -5406,7 +5456,7 @@
         <v>33</v>
       </c>
       <c r="BU16" s="4" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="BV16" s="4"/>
       <c r="BW16" s="4"/>
@@ -6486,7 +6536,7 @@
         <v>33</v>
       </c>
       <c r="BU20" s="4" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="BV20" s="4"/>
       <c r="BW20" s="4"/>
@@ -7026,7 +7076,7 @@
         <v>33</v>
       </c>
       <c r="BU22" s="4" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="BV22" s="4"/>
       <c r="BW22" s="4"/>
@@ -9517,69 +9567,94 @@
     <sortCondition ref="B3:B31"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 BE3:DG31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31">
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
+  <conditionalFormatting sqref="D3:AB3 K3:L31 AC3:AQ31 AS3:AZ31 D4:N5 O4:AB31 BA5:BA31 D6:J31 M6:N31 BC11:BD31 BE3:DG31">
+    <cfRule type="cellIs" dxfId="17" priority="20" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ31">
-    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="16" priority="19" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB12">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB16:BB18">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB25">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE3:BE31">
-    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BE3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG3:BG31">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="11" priority="12" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BG3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI7">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI12">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI20">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BI20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM1:BM1048576">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BM1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN3:BN31">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BN3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS30">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BS30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU12">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BU12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU8">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BU8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU22">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BU22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU20">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BU20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU16">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BS30)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BU16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
